--- a/prospeccao/prospeccao-rvland.xlsx
+++ b/prospeccao/prospeccao-rvland.xlsx
@@ -15,8 +15,8 @@
     <sheet name="Avisos" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leads'!$A$4:$N$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Prioridade'!$A$4:$N$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leads'!$A$4:$O$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Prioridade'!$A$4:$O$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Instagram'!$A$4:$I$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +29,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -99,6 +99,12 @@
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -149,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -197,6 +203,9 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="3" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -207,6 +216,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1738,7 +1750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1747,14 +1759,15 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="62" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="62" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1767,7 +1780,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ordenado por potencial. Cada nota de site saiu da avaliação visual do screenshot, não de heurística.</t>
+          <t>Ordenado por potencial. Site, print, Instagram e e-mail são clicáveis: confira cada avaliação você mesmo.</t>
         </is>
       </c>
     </row>
@@ -1799,45 +1812,50 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>Site</t>
+          <t>Site (clique)</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
+          <t>Print do site</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
           <t>Nota site</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>Feito em</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>Booking</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>Copyright</t>
         </is>
       </c>
-      <c r="K4" s="10" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
+          <t>Instagram (clique)</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
           <t>Seguidores</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr">
-        <is>
-          <t>E-mail</t>
-        </is>
-      </c>
       <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>E-mail (clique)</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
         <is>
           <t>Ângulo de abordagem</t>
         </is>
@@ -1867,85 +1885,95 @@
           <t>Columbus, OH</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>macronmobile.com</t>
         </is>
       </c>
-      <c r="G5" s="21" t="n">
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="K5" s="22" t="inlineStr"/>
-      <c r="L5" s="23" t="inlineStr"/>
-      <c r="M5" s="22" t="inlineStr"/>
-      <c r="N5" s="24" t="inlineStr">
+      <c r="L5" s="22" t="inlineStr"/>
+      <c r="M5" s="24" t="inlineStr"/>
+      <c r="N5" s="22" t="inlineStr"/>
+      <c r="O5" s="25" t="inlineStr">
         <is>
           <t>Site de 2013 com botoes bisotados; detailing premium (pacotes de USD 350) = tem caixa; redesign completo + booking</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="n">
+      <c r="A6" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>Quente</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Octopus Car Washes in Florida</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>car wash</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>octopuscarwashflorida.com</t>
         </is>
       </c>
-      <c r="G6" s="25" t="n">
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H6" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="26" t="inlineStr">
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I6" s="26" t="inlineStr">
+      <c r="J6" s="27" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J6" s="26" t="inlineStr"/>
-      <c r="K6" s="26" t="inlineStr"/>
+      <c r="K6" s="27" t="inlineStr"/>
       <c r="L6" s="27" t="inlineStr"/>
-      <c r="M6" s="26" t="inlineStr"/>
-      <c r="N6" s="28" t="inlineStr">
+      <c r="M6" s="29" t="inlineStr"/>
+      <c r="N6" s="27" t="inlineStr"/>
+      <c r="O6" s="30" t="inlineStr">
         <is>
           <t>Layout anos 2000, logo clipart, fundo de bolhas; 2 unidades familiares; redesign + booking</t>
         </is>
@@ -1975,95 +2003,105 @@
           <t>Phoenix, AZ</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>pvcarwash.com</t>
         </is>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J7" s="22" t="inlineStr"/>
       <c r="K7" s="22" t="inlineStr"/>
-      <c r="L7" s="23" t="inlineStr"/>
-      <c r="M7" s="22" t="inlineStr"/>
-      <c r="N7" s="24" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr"/>
+      <c r="M7" s="24" t="inlineStr"/>
+      <c r="N7" s="22" t="inlineStr"/>
+      <c r="O7" s="25" t="inlineStr">
         <is>
           <t>Template generico ~2010, 1 unidade + loja de conveniencia; redesign completo</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="n">
+      <c r="A8" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Quente</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Curbside Mobile Detailing®</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>detailing</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>Columbus, OH</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>curbsidemobiledetailing.com</t>
         </is>
       </c>
-      <c r="G8" s="25" t="n">
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H8" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="26" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I8" s="26" t="inlineStr">
+      <c r="J8" s="27" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J8" s="26" t="inlineStr">
+      <c r="K8" s="27" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K8" s="26" t="inlineStr">
+      <c r="L8" s="28" t="inlineStr">
         <is>
           <t>@curbsidemobiledetailing</t>
         </is>
       </c>
-      <c r="L8" s="27" t="n">
+      <c r="M8" s="29" t="n">
         <v>1583</v>
       </c>
-      <c r="M8" s="26" t="inlineStr">
+      <c r="N8" s="28" t="inlineStr">
         <is>
           <t>info@curbsidemobiledetailing.com</t>
         </is>
       </c>
-      <c r="N8" s="28" t="inlineStr">
+      <c r="O8" s="30" t="inlineStr">
         <is>
           <t>No ar desde 2001, layout 2012, embed YouTube antigo; historia forte pra contar num site novo</t>
         </is>
@@ -2093,103 +2131,113 @@
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>championshipmartialarts.com</t>
         </is>
       </c>
-      <c r="G9" s="21" t="n">
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J9" s="22" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr"/>
-      <c r="L9" s="23" t="inlineStr"/>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="L9" s="22" t="inlineStr"/>
+      <c r="M9" s="24" t="inlineStr"/>
+      <c r="N9" s="23" t="inlineStr">
         <is>
           <t>p.paquet@d-a-m.ca / holsej@pakskarate.com / capecoral@randori-pro.com</t>
         </is>
       </c>
-      <c r="N9" s="24" t="inlineStr">
+      <c r="O9" s="25" t="inlineStr">
         <is>
           <t>Hero quebrado (secao em branco, form solto); multi-unidades em Orlando; consertar = venda facil de mostrar</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="n">
+      <c r="A10" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>Quente</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>ᐅ #1 Mobile Pet Grooming in Doral, Flori</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>pet grooming</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>purrfectgrooming.pet</t>
         </is>
       </c>
-      <c r="G10" s="25" t="n">
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="26" t="inlineStr">
+      <c r="I10" s="27" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I10" s="26" t="inlineStr">
+      <c r="J10" s="27" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J10" s="26" t="inlineStr">
+      <c r="K10" s="27" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="K10" s="26" t="inlineStr">
+      <c r="L10" s="28" t="inlineStr">
         <is>
           <t>@purrfectgrooming.pet</t>
         </is>
       </c>
-      <c r="L10" s="27" t="n">
+      <c r="M10" s="29" t="n">
         <v>4980</v>
       </c>
-      <c r="M10" s="26" t="inlineStr">
+      <c r="N10" s="28" t="inlineStr">
         <is>
           <t>contactus@purrfectgrooming.pet</t>
         </is>
       </c>
-      <c r="N10" s="28" t="inlineStr">
+      <c r="O10" s="30" t="inlineStr">
         <is>
           <t>Hero quebrado com sobreposicao de logo; frota adesivada (investe em marca); ATENCAO: sede em Doral/Miami</t>
         </is>
@@ -2219,93 +2267,103 @@
           <t>Kansas City, MO</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>choicetreeservicekc.com</t>
         </is>
       </c>
-      <c r="G11" s="21" t="n">
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="J11" s="22" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J11" s="22" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="K11" s="22" t="inlineStr"/>
-      <c r="L11" s="23" t="inlineStr"/>
-      <c r="M11" s="22" t="inlineStr"/>
-      <c r="N11" s="24" t="inlineStr">
+      <c r="L11" s="22" t="inlineStr"/>
+      <c r="M11" s="24" t="inlineStr"/>
+      <c r="N11" s="22" t="inlineStr"/>
+      <c r="O11" s="25" t="inlineStr">
         <is>
           <t>Copyright 2011, template bootstrap velho, form denso; negocio real com 2 telefones</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="n">
+      <c r="A12" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>Morno</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>Phoenix Auto Repair</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>auto repair</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>Phoenix, AZ</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>phoenixautoshop.com</t>
         </is>
       </c>
-      <c r="G12" s="25" t="n">
+      <c r="G12" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H12" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="26" t="inlineStr">
+      <c r="I12" s="27" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I12" s="26" t="inlineStr">
+      <c r="J12" s="27" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J12" s="26" t="inlineStr">
+      <c r="K12" s="27" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K12" s="26" t="inlineStr"/>
       <c r="L12" s="27" t="inlineStr"/>
-      <c r="M12" s="26" t="inlineStr">
+      <c r="M12" s="29" t="inlineStr"/>
+      <c r="N12" s="28" t="inlineStr">
         <is>
           <t>mickey@phoenixautoshop.com</t>
         </is>
       </c>
-      <c r="N12" s="28" t="inlineStr">
+      <c r="O12" s="30" t="inlineStr">
         <is>
           <t>Divi roxo datado ~2015; oficina familiar desde 1979; email do dono (mickey@) exposto no site</t>
         </is>
@@ -2335,85 +2393,95 @@
           <t>Phoenix, AZ</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>touchlesscarwash.com</t>
         </is>
       </c>
-      <c r="G13" s="21" t="n">
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr"/>
-      <c r="L13" s="23" t="inlineStr"/>
-      <c r="M13" s="22" t="inlineStr"/>
-      <c r="N13" s="24" t="inlineStr">
+      <c r="L13" s="22" t="inlineStr"/>
+      <c r="M13" s="24" t="inlineStr"/>
+      <c r="N13" s="22" t="inlineStr"/>
+      <c r="O13" s="25" t="inlineStr">
         <is>
           <t>Visual datado, video com texto arial; rede local pequena de Phoenix</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="n">
+      <c r="A14" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>Morno</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>San Antonio Fence Company</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>fencing</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
       </c>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>sanantoniofencecompany.net</t>
         </is>
       </c>
-      <c r="G14" s="25" t="n">
+      <c r="G14" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="26" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t>Weebly</t>
         </is>
       </c>
-      <c r="I14" s="26" t="inlineStr">
+      <c r="J14" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J14" s="26" t="inlineStr"/>
-      <c r="K14" s="26" t="inlineStr"/>
+      <c r="K14" s="27" t="inlineStr"/>
       <c r="L14" s="27" t="inlineStr"/>
-      <c r="M14" s="26" t="inlineStr"/>
-      <c r="N14" s="28" t="inlineStr">
+      <c r="M14" s="29" t="inlineStr"/>
+      <c r="N14" s="27" t="inlineStr"/>
+      <c r="O14" s="30" t="inlineStr">
         <is>
           <t>Weebly DIY, tipografia generica, fotos reais; dono fez sozinho</t>
         </is>
@@ -2443,99 +2511,109 @@
           <t>Boise, ID</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>westernhvac.com</t>
         </is>
       </c>
-      <c r="G15" s="21" t="n">
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>Squarespace</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="L15" s="23" t="inlineStr">
         <is>
           <t>@westernhvac</t>
         </is>
       </c>
-      <c r="L15" s="23" t="n">
+      <c r="M15" s="24" t="n">
         <v>2281</v>
       </c>
-      <c r="M15" s="22" t="inlineStr">
+      <c r="N15" s="23" t="inlineStr">
         <is>
           <t>csr@westernhvac.com / tom@westernhvac.com / max@westernhvac.com</t>
         </is>
       </c>
-      <c r="N15" s="24" t="inlineStr">
+      <c r="O15" s="25" t="inlineStr">
         <is>
           <t>Logo 3D anos 2000, botoes de ticket; desde 1967, Carrier dealer = caixa; decisao pode ser lenta</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="n">
+      <c r="A16" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>Morno</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>Landscape Company</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>landscaping</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>Columbus, OH</t>
         </is>
       </c>
-      <c r="F16" s="26" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>sciotolandscaping.com</t>
         </is>
       </c>
-      <c r="G16" s="25" t="n">
+      <c r="G16" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H16" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H16" s="26" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I16" s="26" t="inlineStr">
+      <c r="J16" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J16" s="26" t="inlineStr"/>
-      <c r="K16" s="26" t="inlineStr"/>
+      <c r="K16" s="27" t="inlineStr"/>
       <c r="L16" s="27" t="inlineStr"/>
-      <c r="M16" s="26" t="inlineStr">
+      <c r="M16" s="29" t="inlineStr"/>
+      <c r="N16" s="28" t="inlineStr">
         <is>
           <t>info@sciotolandscaping.com</t>
         </is>
       </c>
-      <c r="N16" s="28" t="inlineStr">
+      <c r="O16" s="30" t="inlineStr">
         <is>
           <t>Template 2012 com foto de banco de imagem; info@ visivel no header</t>
         </is>
@@ -2565,103 +2643,113 @@
           <t>Charlotte, NC</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>straightedgepaintingpros.com</t>
         </is>
       </c>
-      <c r="G17" s="21" t="n">
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="J17" s="22" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="K17" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K17" s="22" t="inlineStr"/>
-      <c r="L17" s="23" t="inlineStr"/>
-      <c r="M17" s="22" t="inlineStr">
+      <c r="L17" s="22" t="inlineStr"/>
+      <c r="M17" s="24" t="inlineStr"/>
+      <c r="N17" s="23" t="inlineStr">
         <is>
           <t>straightedgepp@gmail.com</t>
         </is>
       </c>
-      <c r="N17" s="24" t="inlineStr">
+      <c r="O17" s="25" t="inlineStr">
         <is>
           <t>Logo clipart, WP basico; 49 reviews 4.8 = negocio bom com site fraco</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="n">
+      <c r="A18" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>Morno</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>All Creatures Pet Grooming</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>pet grooming</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>allcreaturespetgrooming.com</t>
         </is>
       </c>
-      <c r="G18" s="25" t="n">
+      <c r="G18" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H18" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H18" s="26" t="inlineStr">
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>Wix</t>
         </is>
       </c>
-      <c r="I18" s="26" t="inlineStr">
+      <c r="J18" s="27" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J18" s="26" t="inlineStr">
+      <c r="K18" s="27" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K18" s="26" t="inlineStr">
+      <c r="L18" s="28" t="inlineStr">
         <is>
           <t>@allcreaturespetgrooming</t>
         </is>
       </c>
-      <c r="L18" s="27" t="n">
+      <c r="M18" s="29" t="n">
         <v>3277</v>
       </c>
-      <c r="M18" s="26" t="inlineStr">
+      <c r="N18" s="28" t="inlineStr">
         <is>
           <t>info@allcreaturespetgrooming.com</t>
         </is>
       </c>
-      <c r="N18" s="28" t="inlineStr">
+      <c r="O18" s="30" t="inlineStr">
         <is>
           <t>Wix DIY com logo duplicado gigante e layout desalinhado; tem booking</t>
         </is>
@@ -2691,99 +2779,109 @@
           <t>Kansas City, MO</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>bloombakingco.com</t>
         </is>
       </c>
-      <c r="G19" s="21" t="n">
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J19" s="22" t="inlineStr">
+      <c r="K19" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K19" s="22" t="inlineStr">
+      <c r="L19" s="23" t="inlineStr">
         <is>
           <t>@bloombakingco</t>
         </is>
       </c>
-      <c r="L19" s="23" t="n">
+      <c r="M19" s="24" t="n">
         <v>4204</v>
       </c>
-      <c r="M19" s="22" t="inlineStr"/>
-      <c r="N19" s="24" t="inlineStr">
+      <c r="N19" s="22" t="inlineStr"/>
+      <c r="O19" s="25" t="inlineStr">
         <is>
           <t>Layout ~2015 (Duda), logo simples; padaria artesanal com IG</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="n">
+      <c r="A20" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>Morno</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>Car wash in Tampa</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>car wash</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>Tampa, FL</t>
         </is>
       </c>
-      <c r="F20" s="26" t="inlineStr">
+      <c r="F20" s="28" t="inlineStr">
         <is>
           <t>bluswancarwashtampa.com</t>
         </is>
       </c>
-      <c r="G20" s="25" t="n">
+      <c r="G20" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H20" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H20" s="26" t="inlineStr">
+      <c r="I20" s="27" t="inlineStr">
         <is>
           <t>GoDaddy</t>
         </is>
       </c>
-      <c r="I20" s="26" t="inlineStr">
+      <c r="J20" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J20" s="26" t="inlineStr">
+      <c r="K20" s="27" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K20" s="26" t="inlineStr"/>
       <c r="L20" s="27" t="inlineStr"/>
-      <c r="M20" s="26" t="inlineStr">
+      <c r="M20" s="29" t="inlineStr"/>
+      <c r="N20" s="28" t="inlineStr">
         <is>
           <t>bluswancarwash@gmail.com</t>
         </is>
       </c>
-      <c r="N20" s="28" t="inlineStr">
+      <c r="O20" s="30" t="inlineStr">
         <is>
           <t>GoDaddy DIY, 1 unidade; template razoavel mas generico</t>
         </is>
@@ -2813,95 +2911,105 @@
           <t>San Antonio, TX</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>alamofencesa.com</t>
         </is>
       </c>
-      <c r="G21" s="21" t="n">
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="J21" s="22" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J21" s="22" t="inlineStr"/>
-      <c r="K21" s="22" t="inlineStr">
+      <c r="K21" s="22" t="inlineStr"/>
+      <c r="L21" s="23" t="inlineStr">
         <is>
           <t>@alamofencesa</t>
         </is>
       </c>
-      <c r="L21" s="23" t="n">
+      <c r="M21" s="24" t="n">
         <v>88</v>
       </c>
-      <c r="M21" s="22" t="inlineStr">
+      <c r="N21" s="23" t="inlineStr">
         <is>
           <t>customerservice@alamofencesa.com</t>
         </is>
       </c>
-      <c r="N21" s="24" t="inlineStr">
+      <c r="O21" s="25" t="inlineStr">
         <is>
           <t>Layout centrado antigo; customerservice@ exposto; negocio estabelecido</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="n">
+      <c r="A22" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="27" t="inlineStr">
         <is>
           <t>Morno</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
         <is>
           <t>Boise HVAC</t>
         </is>
       </c>
-      <c r="D22" s="26" t="inlineStr">
+      <c r="D22" s="27" t="inlineStr">
         <is>
           <t>hvac</t>
         </is>
       </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="E22" s="27" t="inlineStr">
         <is>
           <t>Boise, ID</t>
         </is>
       </c>
-      <c r="F22" s="26" t="inlineStr">
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>ims365hvac.com</t>
         </is>
       </c>
-      <c r="G22" s="25" t="n">
+      <c r="G22" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H22" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H22" s="26" t="inlineStr">
+      <c r="I22" s="27" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I22" s="26" t="inlineStr">
+      <c r="J22" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J22" s="26" t="inlineStr"/>
-      <c r="K22" s="26" t="inlineStr"/>
+      <c r="K22" s="27" t="inlineStr"/>
       <c r="L22" s="27" t="inlineStr"/>
-      <c r="M22" s="26" t="inlineStr">
+      <c r="M22" s="29" t="inlineStr"/>
+      <c r="N22" s="28" t="inlineStr">
         <is>
           <t>service@ims365hvac.com</t>
         </is>
       </c>
-      <c r="N22" s="28" t="inlineStr">
+      <c r="O22" s="30" t="inlineStr">
         <is>
           <t>WP generico, hero cru; empresa 25+ anos</t>
         </is>
@@ -2931,101 +3039,111 @@
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>martialartsworldorlando.com</t>
         </is>
       </c>
-      <c r="G23" s="21" t="n">
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="J23" s="22" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J23" s="22" t="inlineStr"/>
-      <c r="K23" s="22" t="inlineStr">
+      <c r="K23" s="22" t="inlineStr"/>
+      <c r="L23" s="23" t="inlineStr">
         <is>
           <t>@maworlando</t>
         </is>
       </c>
-      <c r="L23" s="23" t="n">
+      <c r="M23" s="24" t="n">
         <v>1049</v>
       </c>
-      <c r="M23" s="22" t="inlineStr">
+      <c r="N23" s="23" t="inlineStr">
         <is>
           <t>orlandoadmin@mawus.com</t>
         </is>
       </c>
-      <c r="N23" s="24" t="inlineStr">
+      <c r="O23" s="25" t="inlineStr">
         <is>
           <t>Logo anos 90, layout mediano; academia local com programas</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="n">
+      <c r="A24" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>Morno</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C24" s="27" t="inlineStr">
         <is>
           <t>Power Wash Pro Plus</t>
         </is>
       </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="D24" s="27" t="inlineStr">
         <is>
           <t>pressure washing</t>
         </is>
       </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="E24" s="27" t="inlineStr">
         <is>
           <t>Jacksonville, FL</t>
         </is>
       </c>
-      <c r="F24" s="26" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>powerwashproplus.com</t>
         </is>
       </c>
-      <c r="G24" s="25" t="n">
+      <c r="G24" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H24" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H24" s="26" t="inlineStr">
+      <c r="I24" s="27" t="inlineStr">
         <is>
           <t>Squarespace</t>
         </is>
       </c>
-      <c r="I24" s="26" t="inlineStr">
+      <c r="J24" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J24" s="26" t="inlineStr"/>
-      <c r="K24" s="26" t="inlineStr">
+      <c r="K24" s="27" t="inlineStr"/>
+      <c r="L24" s="28" t="inlineStr">
         <is>
           <t>@powerwashproplus</t>
         </is>
       </c>
-      <c r="L24" s="27" t="n">
+      <c r="M24" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="M24" s="26" t="inlineStr">
+      <c r="N24" s="28" t="inlineStr">
         <is>
           <t>powerwashproplus@gmail.com</t>
         </is>
       </c>
-      <c r="N24" s="28" t="inlineStr">
+      <c r="O24" s="30" t="inlineStr">
         <is>
           <t>Squarespace generico, logo clipart, hero fraco; facil mostrar upgrade</t>
         </is>
@@ -3055,109 +3173,119 @@
           <t>Columbus, OH</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>tatsbywes.com</t>
         </is>
       </c>
-      <c r="G25" s="21" t="n">
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="J25" s="22" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J25" s="22" t="inlineStr">
+      <c r="K25" s="22" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K25" s="22" t="inlineStr">
+      <c r="L25" s="23" t="inlineStr">
         <is>
           <t>@wes_tattoos_columbus</t>
         </is>
       </c>
-      <c r="L25" s="23" t="n">
+      <c r="M25" s="24" t="n">
         <v>11000</v>
       </c>
-      <c r="M25" s="22" t="inlineStr">
+      <c r="N25" s="23" t="inlineStr">
         <is>
           <t>tatsbywes97@gmail.com</t>
         </is>
       </c>
-      <c r="N25" s="24" t="inlineStr">
+      <c r="O25" s="25" t="inlineStr">
         <is>
           <t>Artista solo desde 1997; site simples escuro; decisao rapida, IG e a vida do tatuador</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="n">
+      <c r="A26" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>Frio</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C26" s="27" t="inlineStr">
         <is>
           <t>Bubble Down Car Wash Tampa Bay</t>
         </is>
       </c>
-      <c r="D26" s="26" t="inlineStr">
+      <c r="D26" s="27" t="inlineStr">
         <is>
           <t>car wash</t>
         </is>
       </c>
-      <c r="E26" s="26" t="inlineStr">
+      <c r="E26" s="27" t="inlineStr">
         <is>
           <t>Tampa, FL</t>
         </is>
       </c>
-      <c r="F26" s="26" t="inlineStr">
+      <c r="F26" s="28" t="inlineStr">
         <is>
           <t>bubbledown.com</t>
         </is>
       </c>
-      <c r="G26" s="25" t="n">
+      <c r="G26" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H26" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H26" s="26" t="inlineStr">
+      <c r="I26" s="27" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I26" s="26" t="inlineStr">
+      <c r="J26" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J26" s="26" t="inlineStr">
+      <c r="K26" s="27" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="K26" s="26" t="inlineStr">
+      <c r="L26" s="28" t="inlineStr">
         <is>
           <t>@bubbledowncarwash</t>
         </is>
       </c>
-      <c r="L26" s="27" t="n">
+      <c r="M26" s="29" t="n">
         <v>3598</v>
       </c>
-      <c r="M26" s="26" t="inlineStr">
+      <c r="N26" s="28" t="inlineStr">
         <is>
           <t>info@bubbledown.com</t>
         </is>
       </c>
-      <c r="N26" s="28" t="inlineStr">
+      <c r="O26" s="30" t="inlineStr">
         <is>
           <t>Site ok porem copyright 2016; IG ativo 3.5k; abordagem por relacionamento</t>
         </is>
@@ -3187,99 +3315,109 @@
           <t>San Antonio, TX</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>gsfence.com</t>
         </is>
       </c>
-      <c r="G27" s="21" t="n">
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="I27" s="22" t="inlineStr">
         <is>
           <t>Squarespace</t>
         </is>
       </c>
-      <c r="I27" s="22" t="inlineStr">
+      <c r="J27" s="22" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J27" s="22" t="inlineStr">
+      <c r="K27" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K27" s="22" t="inlineStr"/>
-      <c r="L27" s="23" t="inlineStr"/>
-      <c r="M27" s="22" t="inlineStr">
+      <c r="L27" s="22" t="inlineStr"/>
+      <c r="M27" s="24" t="inlineStr"/>
+      <c r="N27" s="23" t="inlineStr">
         <is>
           <t>gsfencecompany@gmail.com</t>
         </is>
       </c>
-      <c r="N27" s="24" t="inlineStr">
+      <c r="O27" s="25" t="inlineStr">
         <is>
           <t>Site decente mas email no Gmail (DIY vibe); familia</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="n">
+      <c r="A28" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>Frio</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C28" s="27" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>landscaping</t>
         </is>
       </c>
-      <c r="E28" s="26" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>Columbus, OH</t>
         </is>
       </c>
-      <c r="F28" s="26" t="inlineStr">
+      <c r="F28" s="28" t="inlineStr">
         <is>
           <t>buckandsons.com</t>
         </is>
       </c>
-      <c r="G28" s="25" t="n">
+      <c r="G28" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H28" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="26" t="inlineStr">
+      <c r="I28" s="27" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I28" s="26" t="inlineStr">
+      <c r="J28" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J28" s="26" t="inlineStr"/>
-      <c r="K28" s="26" t="inlineStr">
+      <c r="K28" s="27" t="inlineStr"/>
+      <c r="L28" s="28" t="inlineStr">
         <is>
           <t>@buck_and_sons</t>
         </is>
       </c>
-      <c r="L28" s="27" t="n">
+      <c r="M28" s="29" t="n">
         <v>827</v>
       </c>
-      <c r="M28" s="26" t="inlineStr">
+      <c r="N28" s="28" t="inlineStr">
         <is>
           <t>greatoutdoors@buckandsons.com</t>
         </is>
       </c>
-      <c r="N28" s="28" t="inlineStr">
+      <c r="O28" s="30" t="inlineStr">
         <is>
           <t>Desde 1971, site funcional porem datado; empresa grande familiar</t>
         </is>
@@ -3309,105 +3447,115 @@
           <t>Nashville, TN</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>serenitynashville.com</t>
         </is>
       </c>
-      <c r="G29" s="21" t="n">
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="I29" s="22" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I29" s="22" t="inlineStr">
+      <c r="J29" s="22" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J29" s="22" t="inlineStr">
+      <c r="K29" s="22" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K29" s="22" t="inlineStr">
+      <c r="L29" s="23" t="inlineStr">
         <is>
           <t>@serenitynashville</t>
         </is>
       </c>
-      <c r="L29" s="23" t="n">
+      <c r="M29" s="24" t="n">
         <v>346</v>
       </c>
-      <c r="M29" s="22" t="inlineStr">
+      <c r="N29" s="23" t="inlineStr">
         <is>
           <t>info@serenitynashville.com</t>
         </is>
       </c>
-      <c r="N29" s="24" t="inlineStr">
+      <c r="O29" s="25" t="inlineStr">
         <is>
           <t>Site limpo mas datado (2022); nail bar bonito</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="n">
+      <c r="A30" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>Frio</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C30" s="27" t="inlineStr">
         <is>
           <t>Interior &amp; Exterior Painting Contractors</t>
         </is>
       </c>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="D30" s="27" t="inlineStr">
         <is>
           <t>painting</t>
         </is>
       </c>
-      <c r="E30" s="26" t="inlineStr">
+      <c r="E30" s="27" t="inlineStr">
         <is>
           <t>Charlotte, NC</t>
         </is>
       </c>
-      <c r="F30" s="26" t="inlineStr">
+      <c r="F30" s="28" t="inlineStr">
         <is>
           <t>paintingcharlotte.com</t>
         </is>
       </c>
-      <c r="G30" s="25" t="n">
+      <c r="G30" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H30" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="26" t="inlineStr">
+      <c r="I30" s="27" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I30" s="26" t="inlineStr">
+      <c r="J30" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J30" s="26" t="inlineStr"/>
-      <c r="K30" s="26" t="inlineStr">
+      <c r="K30" s="27" t="inlineStr"/>
+      <c r="L30" s="28" t="inlineStr">
         <is>
           <t>@propaintingcharlotte</t>
         </is>
       </c>
-      <c r="L30" s="27" t="n">
+      <c r="M30" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="M30" s="26" t="inlineStr">
+      <c r="N30" s="28" t="inlineStr">
         <is>
           <t>info@propaintingcharlotte.com</t>
         </is>
       </c>
-      <c r="N30" s="28" t="inlineStr">
+      <c r="O30" s="30" t="inlineStr">
         <is>
           <t>Logo anos 2000, layout denso; info@ visivel</t>
         </is>
@@ -3437,103 +3585,113 @@
           <t>Jacksonville, FL</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>jetexterior.com</t>
         </is>
       </c>
-      <c r="G31" s="21" t="n">
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="I31" s="22" t="inlineStr">
         <is>
           <t>Wix</t>
         </is>
       </c>
-      <c r="I31" s="22" t="inlineStr">
+      <c r="J31" s="22" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J31" s="22" t="inlineStr">
+      <c r="K31" s="22" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K31" s="22" t="inlineStr">
+      <c r="L31" s="23" t="inlineStr">
         <is>
           <t>@jet_exterior</t>
         </is>
       </c>
-      <c r="L31" s="23" t="n">
+      <c r="M31" s="24" t="n">
         <v>651</v>
       </c>
-      <c r="M31" s="22" t="inlineStr">
+      <c r="N31" s="23" t="inlineStr">
         <is>
           <t>jetjexcontact@gmail.com / smm@jetexterior.com</t>
         </is>
       </c>
-      <c r="N31" s="24" t="inlineStr">
+      <c r="O31" s="25" t="inlineStr">
         <is>
           <t>Wix razoavel, logo fraco; IG 651</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="25" t="n">
+      <c r="A32" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B32" s="26" t="inlineStr">
+      <c r="B32" s="27" t="inlineStr">
         <is>
           <t>Frio</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C32" s="27" t="inlineStr">
         <is>
           <t>Tree Care Company</t>
         </is>
       </c>
-      <c r="D32" s="26" t="inlineStr">
+      <c r="D32" s="27" t="inlineStr">
         <is>
           <t>tree service</t>
         </is>
       </c>
-      <c r="E32" s="26" t="inlineStr">
+      <c r="E32" s="27" t="inlineStr">
         <is>
           <t>Kansas City, MO</t>
         </is>
       </c>
-      <c r="F32" s="26" t="inlineStr">
+      <c r="F32" s="28" t="inlineStr">
         <is>
           <t>countryclubtreeservice.com</t>
         </is>
       </c>
-      <c r="G32" s="25" t="n">
+      <c r="G32" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H32" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="H32" s="26" t="inlineStr">
+      <c r="I32" s="27" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I32" s="26" t="inlineStr">
+      <c r="J32" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J32" s="26" t="inlineStr">
+      <c r="K32" s="27" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K32" s="26" t="inlineStr"/>
       <c r="L32" s="27" t="inlineStr"/>
-      <c r="M32" s="26" t="inlineStr">
+      <c r="M32" s="29" t="inlineStr"/>
+      <c r="N32" s="28" t="inlineStr">
         <is>
           <t>cctree3@yahoo.com</t>
         </is>
       </c>
-      <c r="N32" s="28" t="inlineStr">
+      <c r="O32" s="30" t="inlineStr">
         <is>
           <t>Desde 1957; template funcional datado-ish</t>
         </is>
@@ -3563,101 +3721,111 @@
           <t>Kansas City, MO</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>mclainskc.com</t>
         </is>
       </c>
-      <c r="G33" s="21" t="n">
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H33" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="H33" s="22" t="inlineStr">
+      <c r="I33" s="22" t="inlineStr">
         <is>
           <t>Squarespace</t>
         </is>
       </c>
-      <c r="I33" s="22" t="inlineStr">
+      <c r="J33" s="22" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J33" s="22" t="inlineStr"/>
-      <c r="K33" s="22" t="inlineStr">
+      <c r="K33" s="22" t="inlineStr"/>
+      <c r="L33" s="23" t="inlineStr">
         <is>
           <t>@mclainsmarketkc</t>
         </is>
       </c>
-      <c r="L33" s="23" t="n">
+      <c r="M33" s="24" t="n">
         <v>27000</v>
       </c>
-      <c r="M33" s="22" t="inlineStr"/>
-      <c r="N33" s="24" t="inlineStr">
+      <c r="N33" s="22" t="inlineStr"/>
+      <c r="O33" s="25" t="inlineStr">
         <is>
           <t>Squarespace ok, hero com contraste ruim; desde 1945</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="n">
+      <c r="A34" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="B34" s="27" t="inlineStr">
         <is>
           <t>Frio</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="C34" s="27" t="inlineStr">
         <is>
           <t>Squeeky's Car Wash</t>
         </is>
       </c>
-      <c r="D34" s="26" t="inlineStr">
+      <c r="D34" s="27" t="inlineStr">
         <is>
           <t>car wash</t>
         </is>
       </c>
-      <c r="E34" s="26" t="inlineStr">
+      <c r="E34" s="27" t="inlineStr">
         <is>
           <t>Tampa, FL</t>
         </is>
       </c>
-      <c r="F34" s="26" t="inlineStr">
+      <c r="F34" s="28" t="inlineStr">
         <is>
           <t>squeekyscarwash.com</t>
         </is>
       </c>
-      <c r="G34" s="25" t="n">
+      <c r="G34" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H34" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="H34" s="26" t="inlineStr">
+      <c r="I34" s="27" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I34" s="26" t="inlineStr">
+      <c r="J34" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J34" s="26" t="inlineStr">
+      <c r="K34" s="27" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K34" s="26" t="inlineStr">
+      <c r="L34" s="28" t="inlineStr">
         <is>
           <t>@squeekyscarwash</t>
         </is>
       </c>
-      <c r="L34" s="27" t="n">
+      <c r="M34" s="29" t="n">
         <v>927</v>
       </c>
-      <c r="M34" s="26" t="inlineStr">
+      <c r="N34" s="28" t="inlineStr">
         <is>
           <t>support@squeekyscarwash.com</t>
         </is>
       </c>
-      <c r="N34" s="28" t="inlineStr">
+      <c r="O34" s="30" t="inlineStr">
         <is>
           <t>Template moderno ok; pouca dor aparente</t>
         </is>
@@ -3687,105 +3855,115 @@
           <t>San Antonio, TX</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="23" t="inlineStr">
         <is>
           <t>comalfence.com</t>
         </is>
       </c>
-      <c r="G35" s="21" t="n">
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H35" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="I35" s="22" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I35" s="22" t="inlineStr">
+      <c r="J35" s="22" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J35" s="22" t="inlineStr">
+      <c r="K35" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K35" s="22" t="inlineStr">
+      <c r="L35" s="23" t="inlineStr">
         <is>
           <t>@comalfencesa</t>
         </is>
       </c>
-      <c r="L35" s="23" t="n">
+      <c r="M35" s="24" t="n">
         <v>303</v>
       </c>
-      <c r="M35" s="22" t="inlineStr">
+      <c r="N35" s="23" t="inlineStr">
         <is>
           <t>sales@comalfence.com</t>
         </is>
       </c>
-      <c r="N35" s="24" t="inlineStr">
+      <c r="O35" s="25" t="inlineStr">
         <is>
           <t>Razoavel e funcional</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="25" t="n">
+      <c r="A36" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="B36" s="26" t="inlineStr">
+      <c r="B36" s="27" t="inlineStr">
         <is>
           <t>Frio</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C36" s="27" t="inlineStr">
         <is>
           <t>Fitness Gym &amp; Classes in Boise, Idaho</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="D36" s="27" t="inlineStr">
         <is>
           <t>gym</t>
         </is>
       </c>
-      <c r="E36" s="26" t="inlineStr">
+      <c r="E36" s="27" t="inlineStr">
         <is>
           <t>Boise, ID</t>
         </is>
       </c>
-      <c r="F36" s="26" t="inlineStr">
+      <c r="F36" s="28" t="inlineStr">
         <is>
           <t>functionalidaho.com</t>
         </is>
       </c>
-      <c r="G36" s="25" t="n">
+      <c r="G36" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H36" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="H36" s="26" t="inlineStr">
+      <c r="I36" s="27" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I36" s="26" t="inlineStr">
+      <c r="J36" s="27" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J36" s="26" t="inlineStr">
+      <c r="K36" s="27" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K36" s="26" t="inlineStr">
+      <c r="L36" s="28" t="inlineStr">
         <is>
           <t>@functional.idaho</t>
         </is>
       </c>
-      <c r="L36" s="27" t="n">
+      <c r="M36" s="29" t="n">
         <v>15000</v>
       </c>
-      <c r="M36" s="26" t="inlineStr"/>
-      <c r="N36" s="28" t="inlineStr">
+      <c r="N36" s="27" t="inlineStr"/>
+      <c r="O36" s="30" t="inlineStr">
         <is>
           <t>Carregado mas funcional; 630 reviews; familia</t>
         </is>
@@ -3815,107 +3993,117 @@
           <t>Jacksonville, FL</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="23" t="inlineStr">
         <is>
           <t>mcdanielslawncare.com</t>
         </is>
       </c>
-      <c r="G37" s="21" t="n">
+      <c r="G37" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H37" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="H37" s="22" t="inlineStr">
+      <c r="I37" s="22" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I37" s="22" t="inlineStr">
+      <c r="J37" s="22" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J37" s="22" t="inlineStr">
+      <c r="K37" s="22" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="K37" s="22" t="inlineStr">
+      <c r="L37" s="23" t="inlineStr">
         <is>
           <t>@mcdaniels_landscaping</t>
         </is>
       </c>
-      <c r="L37" s="23" t="n">
+      <c r="M37" s="24" t="n">
         <v>186</v>
       </c>
-      <c r="M37" s="22" t="inlineStr">
+      <c r="N37" s="23" t="inlineStr">
         <is>
           <t>mike@mcdanielslawncare.com / krischislett@gmail.com</t>
         </is>
       </c>
-      <c r="N37" s="24" t="inlineStr">
+      <c r="O37" s="25" t="inlineStr">
         <is>
           <t>Site razoavel com bug visual no hero; mike@ exposto</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="25" t="n">
+      <c r="A38" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="B38" s="26" t="inlineStr">
+      <c r="B38" s="27" t="inlineStr">
         <is>
           <t>Frio</t>
         </is>
       </c>
-      <c r="C38" s="26" t="inlineStr">
+      <c r="C38" s="27" t="inlineStr">
         <is>
           <t>Pressure Washing Jacksonville, FL</t>
         </is>
       </c>
-      <c r="D38" s="26" t="inlineStr">
+      <c r="D38" s="27" t="inlineStr">
         <is>
           <t>pressure washing</t>
         </is>
       </c>
-      <c r="E38" s="26" t="inlineStr">
+      <c r="E38" s="27" t="inlineStr">
         <is>
           <t>Jacksonville, FL</t>
         </is>
       </c>
-      <c r="F38" s="26" t="inlineStr">
+      <c r="F38" s="28" t="inlineStr">
         <is>
           <t>pressurewashjacksonvillefl.com</t>
         </is>
       </c>
-      <c r="G38" s="25" t="n">
+      <c r="G38" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H38" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="H38" s="26" t="inlineStr">
+      <c r="I38" s="27" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I38" s="26" t="inlineStr">
+      <c r="J38" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J38" s="26" t="inlineStr">
+      <c r="K38" s="27" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K38" s="26" t="inlineStr">
+      <c r="L38" s="28" t="inlineStr">
         <is>
           <t>@boldwashjacksonville</t>
         </is>
       </c>
-      <c r="L38" s="27" t="inlineStr"/>
-      <c r="M38" s="26" t="inlineStr">
+      <c r="M38" s="29" t="inlineStr"/>
+      <c r="N38" s="28" t="inlineStr">
         <is>
           <t>hello@boldwashjacksonville.com</t>
         </is>
       </c>
-      <c r="N38" s="28" t="inlineStr">
+      <c r="O38" s="30" t="inlineStr">
         <is>
           <t>Site ok generico; IG com 0 seguidores = comecando presenca social</t>
         </is>
@@ -3945,97 +4133,107 @@
           <t>Kansas City, MO</t>
         </is>
       </c>
-      <c r="F39" s="22" t="inlineStr">
+      <c r="F39" s="23" t="inlineStr">
         <is>
           <t>kansascitytreeservices.net</t>
         </is>
       </c>
-      <c r="G39" s="21" t="n">
+      <c r="G39" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H39" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="H39" s="22" t="inlineStr">
+      <c r="I39" s="22" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I39" s="22" t="inlineStr">
+      <c r="J39" s="22" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J39" s="22" t="inlineStr">
+      <c r="K39" s="22" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K39" s="22" t="inlineStr"/>
-      <c r="L39" s="23" t="inlineStr"/>
-      <c r="M39" s="22" t="inlineStr">
+      <c r="L39" s="22" t="inlineStr"/>
+      <c r="M39" s="24" t="inlineStr"/>
+      <c r="N39" s="23" t="inlineStr">
         <is>
           <t>info@kansascitytreeservices.net</t>
         </is>
       </c>
-      <c r="N39" s="24" t="inlineStr">
+      <c r="O39" s="25" t="inlineStr">
         <is>
           <t>SUSPEITA de lead-broker: telefone placeholder 816-555-7890 na foto; verificar se e negocio real</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="25" t="n">
+      <c r="A40" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B40" s="26" t="inlineStr">
+      <c r="B40" s="27" t="inlineStr">
         <is>
           <t>Descartar</t>
         </is>
       </c>
-      <c r="C40" s="26" t="inlineStr">
+      <c r="C40" s="27" t="inlineStr">
         <is>
           <t>Auto Repair Shop Phoenix AZ</t>
         </is>
       </c>
-      <c r="D40" s="26" t="inlineStr">
+      <c r="D40" s="27" t="inlineStr">
         <is>
           <t>auto repair</t>
         </is>
       </c>
-      <c r="E40" s="26" t="inlineStr">
+      <c r="E40" s="27" t="inlineStr">
         <is>
           <t>Phoenix, AZ</t>
         </is>
       </c>
-      <c r="F40" s="26" t="inlineStr">
+      <c r="F40" s="28" t="inlineStr">
         <is>
           <t>autorepairshopphoenix.com</t>
         </is>
       </c>
-      <c r="G40" s="25" t="n">
+      <c r="G40" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H40" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="H40" s="26" t="inlineStr">
+      <c r="I40" s="27" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I40" s="26" t="inlineStr">
+      <c r="J40" s="27" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J40" s="26" t="inlineStr">
+      <c r="K40" s="27" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K40" s="26" t="inlineStr"/>
       <c r="L40" s="27" t="inlineStr"/>
-      <c r="M40" s="26" t="inlineStr">
+      <c r="M40" s="29" t="inlineStr"/>
+      <c r="N40" s="28" t="inlineStr">
         <is>
           <t>info@perezautorepairs.com</t>
         </is>
       </c>
-      <c r="N40" s="28" t="inlineStr">
+      <c r="O40" s="30" t="inlineStr">
         <is>
           <t>Moderno com social proof; desde 1976</t>
         </is>
@@ -4065,91 +4263,101 @@
           <t>Phoenix, AZ</t>
         </is>
       </c>
-      <c r="F41" s="22" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
         <is>
           <t>tbirdauto.com</t>
         </is>
       </c>
-      <c r="G41" s="21" t="n">
+      <c r="G41" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H41" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="H41" s="22" t="inlineStr">
+      <c r="I41" s="22" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I41" s="22" t="inlineStr">
+      <c r="J41" s="22" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J41" s="22" t="inlineStr"/>
       <c r="K41" s="22" t="inlineStr"/>
-      <c r="L41" s="23" t="inlineStr"/>
-      <c r="M41" s="22" t="inlineStr"/>
-      <c r="N41" s="24" t="inlineStr">
+      <c r="L41" s="22" t="inlineStr"/>
+      <c r="M41" s="24" t="inlineStr"/>
+      <c r="N41" s="22" t="inlineStr"/>
+      <c r="O41" s="25" t="inlineStr">
         <is>
           <t>Moderno com fotos reais da equipe</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="25" t="n">
+      <c r="A42" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B42" s="26" t="inlineStr">
+      <c r="B42" s="27" t="inlineStr">
         <is>
           <t>Descartar</t>
         </is>
       </c>
-      <c r="C42" s="26" t="inlineStr">
+      <c r="C42" s="27" t="inlineStr">
         <is>
           <t>Joe’s Express Carwash</t>
         </is>
       </c>
-      <c r="D42" s="26" t="inlineStr">
+      <c r="D42" s="27" t="inlineStr">
         <is>
           <t>car wash</t>
         </is>
       </c>
-      <c r="E42" s="26" t="inlineStr">
+      <c r="E42" s="27" t="inlineStr">
         <is>
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="F42" s="26" t="inlineStr">
+      <c r="F42" s="28" t="inlineStr">
         <is>
           <t>joescarwashes.com</t>
         </is>
       </c>
-      <c r="G42" s="25" t="n">
+      <c r="G42" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H42" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="H42" s="26" t="inlineStr">
+      <c r="I42" s="27" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I42" s="26" t="inlineStr">
+      <c r="J42" s="27" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J42" s="26" t="inlineStr">
+      <c r="K42" s="27" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K42" s="26" t="inlineStr">
+      <c r="L42" s="28" t="inlineStr">
         <is>
           <t>@joescarwashfl</t>
         </is>
       </c>
-      <c r="L42" s="27" t="n">
+      <c r="M42" s="29" t="n">
         <v>57</v>
       </c>
-      <c r="M42" s="26" t="inlineStr"/>
-      <c r="N42" s="28" t="inlineStr">
+      <c r="N42" s="27" t="inlineStr"/>
+      <c r="O42" s="30" t="inlineStr">
         <is>
           <t>Site bom; IG com so 57 seguidores (oportunidade social, nao site)</t>
         </is>
@@ -4179,109 +4387,119 @@
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="F43" s="22" t="inlineStr">
+      <c r="F43" s="23" t="inlineStr">
         <is>
           <t>aquashineexpress.com</t>
         </is>
       </c>
-      <c r="G43" s="21" t="n">
+      <c r="G43" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H43" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="H43" s="22" t="inlineStr">
+      <c r="I43" s="22" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I43" s="22" t="inlineStr">
+      <c r="J43" s="22" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J43" s="22" t="inlineStr">
+      <c r="K43" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K43" s="22" t="inlineStr">
+      <c r="L43" s="23" t="inlineStr">
         <is>
           <t>@aquashineexpress</t>
         </is>
       </c>
-      <c r="L43" s="23" t="n">
+      <c r="M43" s="24" t="n">
         <v>438</v>
       </c>
-      <c r="M43" s="22" t="inlineStr">
+      <c r="N43" s="23" t="inlineStr">
         <is>
           <t>support@aquashineexpress.com</t>
         </is>
       </c>
-      <c r="N43" s="24" t="inlineStr">
+      <c r="O43" s="25" t="inlineStr">
         <is>
           <t>Site moderno bom</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="25" t="n">
+      <c r="A44" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B44" s="26" t="inlineStr">
+      <c r="B44" s="27" t="inlineStr">
         <is>
           <t>Descartar</t>
         </is>
       </c>
-      <c r="C44" s="26" t="inlineStr">
+      <c r="C44" s="27" t="inlineStr">
         <is>
           <t>Woodies Wash Shack</t>
         </is>
       </c>
-      <c r="D44" s="26" t="inlineStr">
+      <c r="D44" s="27" t="inlineStr">
         <is>
           <t>car wash</t>
         </is>
       </c>
-      <c r="E44" s="26" t="inlineStr">
+      <c r="E44" s="27" t="inlineStr">
         <is>
           <t>Tampa, FL</t>
         </is>
       </c>
-      <c r="F44" s="26" t="inlineStr">
+      <c r="F44" s="28" t="inlineStr">
         <is>
           <t>woodieswash.com</t>
         </is>
       </c>
-      <c r="G44" s="25" t="n">
+      <c r="G44" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H44" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="H44" s="26" t="inlineStr">
+      <c r="I44" s="27" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I44" s="26" t="inlineStr">
+      <c r="J44" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J44" s="26" t="inlineStr">
+      <c r="K44" s="27" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K44" s="26" t="inlineStr">
+      <c r="L44" s="28" t="inlineStr">
         <is>
           <t>@woodieswashshack</t>
         </is>
       </c>
-      <c r="L44" s="27" t="n">
+      <c r="M44" s="29" t="n">
         <v>10000</v>
       </c>
-      <c r="M44" s="26" t="inlineStr">
+      <c r="N44" s="28" t="inlineStr">
         <is>
           <t>info@woodieswash.com</t>
         </is>
       </c>
-      <c r="N44" s="28" t="inlineStr">
+      <c r="O44" s="30" t="inlineStr">
         <is>
           <t>Marca forte, 18+ unidades, IG 10K; provavelmente tem agencia</t>
         </is>
@@ -4311,105 +4529,115 @@
           <t>Tampa, FL</t>
         </is>
       </c>
-      <c r="F45" s="22" t="inlineStr">
+      <c r="F45" s="23" t="inlineStr">
         <is>
           <t>bigdanscarwash.com</t>
         </is>
       </c>
-      <c r="G45" s="21" t="n">
+      <c r="G45" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H45" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="H45" s="22" t="inlineStr">
+      <c r="I45" s="22" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I45" s="22" t="inlineStr">
+      <c r="J45" s="22" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J45" s="22" t="inlineStr">
+      <c r="K45" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K45" s="22" t="inlineStr">
+      <c r="L45" s="23" t="inlineStr">
         <is>
           <t>@bigdanscarwash</t>
         </is>
       </c>
-      <c r="L45" s="23" t="n">
+      <c r="M45" s="24" t="n">
         <v>2433</v>
       </c>
-      <c r="M45" s="22" t="inlineStr"/>
-      <c r="N45" s="24" t="inlineStr">
+      <c r="N45" s="22" t="inlineStr"/>
+      <c r="O45" s="25" t="inlineStr">
         <is>
           <t>Site moderno; rede regional</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="25" t="n">
+      <c r="A46" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B46" s="26" t="inlineStr">
+      <c r="B46" s="27" t="inlineStr">
         <is>
           <t>Descartar</t>
         </is>
       </c>
-      <c r="C46" s="26" t="inlineStr">
+      <c r="C46" s="27" t="inlineStr">
         <is>
           <t>Experience AquaSonic Car Wash</t>
         </is>
       </c>
-      <c r="D46" s="26" t="inlineStr">
+      <c r="D46" s="27" t="inlineStr">
         <is>
           <t>car wash</t>
         </is>
       </c>
-      <c r="E46" s="26" t="inlineStr">
+      <c r="E46" s="27" t="inlineStr">
         <is>
           <t>Tampa, FL</t>
         </is>
       </c>
-      <c r="F46" s="26" t="inlineStr">
+      <c r="F46" s="28" t="inlineStr">
         <is>
           <t>aquasoniccarwash.com</t>
         </is>
       </c>
-      <c r="G46" s="25" t="n">
+      <c r="G46" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H46" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="H46" s="26" t="inlineStr">
+      <c r="I46" s="27" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I46" s="26" t="inlineStr">
+      <c r="J46" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J46" s="26" t="inlineStr">
+      <c r="K46" s="27" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K46" s="26" t="inlineStr">
+      <c r="L46" s="28" t="inlineStr">
         <is>
           <t>@aquasoniccarwash</t>
         </is>
       </c>
-      <c r="L46" s="27" t="n">
+      <c r="M46" s="29" t="n">
         <v>1992</v>
       </c>
-      <c r="M46" s="26" t="inlineStr">
+      <c r="N46" s="28" t="inlineStr">
         <is>
           <t>info@aquasoniccarwash.com</t>
         </is>
       </c>
-      <c r="N46" s="28" t="inlineStr">
+      <c r="O46" s="30" t="inlineStr">
         <is>
           <t>Site moderno</t>
         </is>
@@ -4439,101 +4667,111 @@
           <t>San Antonio, TX</t>
         </is>
       </c>
-      <c r="F47" s="22" t="inlineStr">
+      <c r="F47" s="23" t="inlineStr">
         <is>
           <t>johnsonservicescompany.com</t>
         </is>
       </c>
-      <c r="G47" s="21" t="n">
+      <c r="G47" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H47" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="H47" s="22" t="inlineStr">
+      <c r="I47" s="22" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I47" s="22" t="inlineStr">
+      <c r="J47" s="22" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J47" s="22" t="inlineStr">
+      <c r="K47" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K47" s="22" t="inlineStr">
+      <c r="L47" s="23" t="inlineStr">
         <is>
           <t>@Johnsonservicescompany</t>
         </is>
       </c>
-      <c r="L47" s="23" t="n">
+      <c r="M47" s="24" t="n">
         <v>26</v>
       </c>
-      <c r="M47" s="22" t="inlineStr"/>
-      <c r="N47" s="24" t="inlineStr">
+      <c r="N47" s="22" t="inlineStr"/>
+      <c r="O47" s="25" t="inlineStr">
         <is>
           <t>Grande (4 cidades TX), video no hero</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="25" t="n">
+      <c r="A48" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B48" s="26" t="inlineStr">
+      <c r="B48" s="27" t="inlineStr">
         <is>
           <t>Descartar</t>
         </is>
       </c>
-      <c r="C48" s="26" t="inlineStr">
+      <c r="C48" s="27" t="inlineStr">
         <is>
           <t>Idaho Fitness Factory 24/7 Local Gym</t>
         </is>
       </c>
-      <c r="D48" s="26" t="inlineStr">
+      <c r="D48" s="27" t="inlineStr">
         <is>
           <t>gym</t>
         </is>
       </c>
-      <c r="E48" s="26" t="inlineStr">
+      <c r="E48" s="27" t="inlineStr">
         <is>
           <t>Boise, ID</t>
         </is>
       </c>
-      <c r="F48" s="26" t="inlineStr">
+      <c r="F48" s="28" t="inlineStr">
         <is>
           <t>idahofitnessfactory.com</t>
         </is>
       </c>
-      <c r="G48" s="25" t="n">
+      <c r="G48" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H48" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="H48" s="26" t="inlineStr">
+      <c r="I48" s="27" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I48" s="26" t="inlineStr">
+      <c r="J48" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J48" s="26" t="inlineStr"/>
-      <c r="K48" s="26" t="inlineStr">
+      <c r="K48" s="27" t="inlineStr"/>
+      <c r="L48" s="28" t="inlineStr">
         <is>
           <t>@idahofitnessfactory</t>
         </is>
       </c>
-      <c r="L48" s="27" t="n">
+      <c r="M48" s="29" t="n">
         <v>6724</v>
       </c>
-      <c r="M48" s="26" t="inlineStr">
+      <c r="N48" s="28" t="inlineStr">
         <is>
           <t>admin@idahofitnessfactory.com</t>
         </is>
       </c>
-      <c r="N48" s="28" t="inlineStr">
+      <c r="O48" s="30" t="inlineStr">
         <is>
           <t>Moderno; 10+ unidades</t>
         </is>
@@ -4563,109 +4801,119 @@
           <t>Boise, ID</t>
         </is>
       </c>
-      <c r="F49" s="22" t="inlineStr">
+      <c r="F49" s="23" t="inlineStr">
         <is>
           <t>foxhvacpro.com</t>
         </is>
       </c>
-      <c r="G49" s="21" t="n">
+      <c r="G49" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H49" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="H49" s="22" t="inlineStr">
+      <c r="I49" s="22" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I49" s="22" t="inlineStr">
+      <c r="J49" s="22" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J49" s="22" t="inlineStr">
+      <c r="K49" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K49" s="22" t="inlineStr">
+      <c r="L49" s="23" t="inlineStr">
         <is>
           <t>@foxheatingandcooling</t>
         </is>
       </c>
-      <c r="L49" s="23" t="n">
+      <c r="M49" s="24" t="n">
         <v>67</v>
       </c>
-      <c r="M49" s="22" t="inlineStr">
+      <c r="N49" s="23" t="inlineStr">
         <is>
           <t>info@foxhvacpro.com</t>
         </is>
       </c>
-      <c r="N49" s="24" t="inlineStr">
+      <c r="O49" s="25" t="inlineStr">
         <is>
           <t>Moderno, badges 2026</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="25" t="n">
+      <c r="A50" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B50" s="26" t="inlineStr">
+      <c r="B50" s="27" t="inlineStr">
         <is>
           <t>Descartar</t>
         </is>
       </c>
-      <c r="C50" s="26" t="inlineStr">
+      <c r="C50" s="27" t="inlineStr">
         <is>
           <t>Charlotte Paint Squad</t>
         </is>
       </c>
-      <c r="D50" s="26" t="inlineStr">
+      <c r="D50" s="27" t="inlineStr">
         <is>
           <t>painting</t>
         </is>
       </c>
-      <c r="E50" s="26" t="inlineStr">
+      <c r="E50" s="27" t="inlineStr">
         <is>
           <t>Charlotte, NC</t>
         </is>
       </c>
-      <c r="F50" s="26" t="inlineStr">
+      <c r="F50" s="28" t="inlineStr">
         <is>
           <t>charlottepaintsquad.com</t>
         </is>
       </c>
-      <c r="G50" s="25" t="n">
+      <c r="G50" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H50" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="H50" s="26" t="inlineStr">
+      <c r="I50" s="27" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I50" s="26" t="inlineStr">
+      <c r="J50" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J50" s="26" t="inlineStr">
+      <c r="K50" s="27" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K50" s="26" t="inlineStr">
+      <c r="L50" s="28" t="inlineStr">
         <is>
           <t>@charlottepaintsquad</t>
         </is>
       </c>
-      <c r="L50" s="27" t="n">
+      <c r="M50" s="29" t="n">
         <v>894</v>
       </c>
-      <c r="M50" s="26" t="inlineStr">
+      <c r="N50" s="28" t="inlineStr">
         <is>
           <t>paintsquadcharlotte@gmail.com</t>
         </is>
       </c>
-      <c r="N50" s="28" t="inlineStr">
+      <c r="O50" s="30" t="inlineStr">
         <is>
           <t>Lead-gen moderno</t>
         </is>
@@ -4695,103 +4943,113 @@
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="F51" s="22" t="inlineStr">
+      <c r="F51" s="23" t="inlineStr">
         <is>
           <t>groombar.com</t>
         </is>
       </c>
-      <c r="G51" s="21" t="n">
+      <c r="G51" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H51" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="H51" s="22" t="inlineStr">
+      <c r="I51" s="22" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I51" s="22" t="inlineStr">
+      <c r="J51" s="22" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J51" s="22" t="inlineStr">
+      <c r="K51" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K51" s="22" t="inlineStr">
+      <c r="L51" s="23" t="inlineStr">
         <is>
           <t>@groombarsalon</t>
         </is>
       </c>
-      <c r="L51" s="23" t="n">
+      <c r="M51" s="24" t="n">
         <v>343</v>
       </c>
-      <c r="M51" s="22" t="inlineStr">
+      <c r="N51" s="23" t="inlineStr">
         <is>
           <t>info@groombar.com</t>
         </is>
       </c>
-      <c r="N51" s="24" t="inlineStr">
+      <c r="O51" s="25" t="inlineStr">
         <is>
           <t>Moderno; franchising no menu</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="25" t="n">
+      <c r="A52" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B52" s="26" t="inlineStr">
+      <c r="B52" s="27" t="inlineStr">
         <is>
           <t>Descartar</t>
         </is>
       </c>
-      <c r="C52" s="26" t="inlineStr">
+      <c r="C52" s="27" t="inlineStr">
         <is>
           <t>Pressure Washing Jacksonville FL</t>
         </is>
       </c>
-      <c r="D52" s="26" t="inlineStr">
+      <c r="D52" s="27" t="inlineStr">
         <is>
           <t>pressure washing</t>
         </is>
       </c>
-      <c r="E52" s="26" t="inlineStr">
+      <c r="E52" s="27" t="inlineStr">
         <is>
           <t>Jacksonville, FL</t>
         </is>
       </c>
-      <c r="F52" s="26" t="inlineStr">
+      <c r="F52" s="28" t="inlineStr">
         <is>
           <t>coraljaxpressurewashing.com</t>
         </is>
       </c>
-      <c r="G52" s="25" t="n">
+      <c r="G52" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H52" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="H52" s="26" t="inlineStr">
+      <c r="I52" s="27" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I52" s="26" t="inlineStr">
+      <c r="J52" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J52" s="26" t="inlineStr">
+      <c r="K52" s="27" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="K52" s="26" t="inlineStr"/>
       <c r="L52" s="27" t="inlineStr"/>
-      <c r="M52" s="26" t="inlineStr">
+      <c r="M52" s="29" t="inlineStr"/>
+      <c r="N52" s="28" t="inlineStr">
         <is>
           <t>info@coraljaxpressurewashing.com</t>
         </is>
       </c>
-      <c r="N52" s="28" t="inlineStr">
+      <c r="O52" s="30" t="inlineStr">
         <is>
           <t>Site bom com precos claros</t>
         </is>
@@ -4821,97 +5079,107 @@
           <t>Jacksonville, FL</t>
         </is>
       </c>
-      <c r="F53" s="22" t="inlineStr">
+      <c r="F53" s="23" t="inlineStr">
         <is>
           <t>pressurewashinginjacksonvillefl.com</t>
         </is>
       </c>
-      <c r="G53" s="21" t="n">
+      <c r="G53" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H53" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="H53" s="22" t="inlineStr">
+      <c r="I53" s="22" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I53" s="22" t="inlineStr">
+      <c r="J53" s="22" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J53" s="22" t="inlineStr">
+      <c r="K53" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K53" s="22" t="inlineStr"/>
-      <c r="L53" s="23" t="inlineStr"/>
-      <c r="M53" s="22" t="inlineStr">
+      <c r="L53" s="22" t="inlineStr"/>
+      <c r="M53" s="24" t="inlineStr"/>
+      <c r="N53" s="23" t="inlineStr">
         <is>
           <t>info@pressurewashinginjacksonvillefl.com</t>
         </is>
       </c>
-      <c r="N53" s="24" t="inlineStr">
+      <c r="O53" s="25" t="inlineStr">
         <is>
           <t>Moderno decente</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="25" t="n">
+      <c r="A54" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B54" s="26" t="inlineStr">
+      <c r="B54" s="27" t="inlineStr">
         <is>
           <t>Descartar</t>
         </is>
       </c>
-      <c r="C54" s="26" t="inlineStr">
+      <c r="C54" s="27" t="inlineStr">
         <is>
           <t>Pressure Washing Jacksonville FL</t>
         </is>
       </c>
-      <c r="D54" s="26" t="inlineStr">
+      <c r="D54" s="27" t="inlineStr">
         <is>
           <t>pressure washing</t>
         </is>
       </c>
-      <c r="E54" s="26" t="inlineStr">
+      <c r="E54" s="27" t="inlineStr">
         <is>
           <t>Jacksonville, FL</t>
         </is>
       </c>
-      <c r="F54" s="26" t="inlineStr">
+      <c r="F54" s="28" t="inlineStr">
         <is>
           <t>jaxpropressurewash.com</t>
         </is>
       </c>
-      <c r="G54" s="25" t="n">
+      <c r="G54" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H54" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="H54" s="26" t="inlineStr">
+      <c r="I54" s="27" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I54" s="26" t="inlineStr">
+      <c r="J54" s="27" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J54" s="26" t="inlineStr">
+      <c r="K54" s="27" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K54" s="26" t="inlineStr"/>
       <c r="L54" s="27" t="inlineStr"/>
-      <c r="M54" s="26" t="inlineStr">
+      <c r="M54" s="29" t="inlineStr"/>
+      <c r="N54" s="28" t="inlineStr">
         <is>
           <t>hello@jacksonvillewasher.com</t>
         </is>
       </c>
-      <c r="N54" s="28" t="inlineStr">
+      <c r="O54" s="30" t="inlineStr">
         <is>
           <t>Site moderno bonito; hello@ exposto</t>
         </is>
@@ -4941,95 +5209,105 @@
           <t>Kansas City, MO</t>
         </is>
       </c>
-      <c r="F55" s="22" t="inlineStr">
+      <c r="F55" s="23" t="inlineStr">
         <is>
           <t>kcarborist.com</t>
         </is>
       </c>
-      <c r="G55" s="21" t="n">
+      <c r="G55" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H55" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="H55" s="22" t="inlineStr">
+      <c r="I55" s="22" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I55" s="22" t="inlineStr">
+      <c r="J55" s="22" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J55" s="22" t="inlineStr"/>
-      <c r="K55" s="22" t="inlineStr">
+      <c r="K55" s="22" t="inlineStr"/>
+      <c r="L55" s="23" t="inlineStr">
         <is>
           <t>@kcarboristtreecare</t>
         </is>
       </c>
-      <c r="L55" s="23" t="n">
+      <c r="M55" s="24" t="n">
         <v>941</v>
       </c>
-      <c r="M55" s="22" t="inlineStr">
+      <c r="N55" s="23" t="inlineStr">
         <is>
           <t>info@kcarborist.com</t>
         </is>
       </c>
-      <c r="N55" s="24" t="inlineStr">
+      <c r="O55" s="25" t="inlineStr">
         <is>
           <t>Site ok com badges de rating</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="25" t="n">
+      <c r="A56" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B56" s="26" t="inlineStr">
+      <c r="B56" s="27" t="inlineStr">
         <is>
           <t>Descartar</t>
         </is>
       </c>
-      <c r="C56" s="26" t="inlineStr">
+      <c r="C56" s="27" t="inlineStr">
         <is>
           <t>Tree Service in Kansas City</t>
         </is>
       </c>
-      <c r="D56" s="26" t="inlineStr">
+      <c r="D56" s="27" t="inlineStr">
         <is>
           <t>tree service</t>
         </is>
       </c>
-      <c r="E56" s="26" t="inlineStr">
+      <c r="E56" s="27" t="inlineStr">
         <is>
           <t>Kansas City, MO</t>
         </is>
       </c>
-      <c r="F56" s="26" t="inlineStr">
+      <c r="F56" s="28" t="inlineStr">
         <is>
           <t>kctreecareks.com</t>
         </is>
       </c>
-      <c r="G56" s="25" t="n">
+      <c r="G56" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H56" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="H56" s="26" t="inlineStr">
+      <c r="I56" s="27" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I56" s="26" t="inlineStr">
+      <c r="J56" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J56" s="26" t="inlineStr">
+      <c r="K56" s="27" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K56" s="26" t="inlineStr"/>
       <c r="L56" s="27" t="inlineStr"/>
-      <c r="M56" s="26" t="inlineStr"/>
-      <c r="N56" s="28" t="inlineStr">
+      <c r="M56" s="29" t="inlineStr"/>
+      <c r="N56" s="27" t="inlineStr"/>
+      <c r="O56" s="30" t="inlineStr">
         <is>
           <t>Lead-gen competente</t>
         </is>
@@ -5059,99 +5337,109 @@
           <t>Phoenix, AZ</t>
         </is>
       </c>
-      <c r="F57" s="22" t="inlineStr">
+      <c r="F57" s="23" t="inlineStr">
         <is>
           <t>azautoshop.com</t>
         </is>
       </c>
-      <c r="G57" s="21" t="n">
+      <c r="G57" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H57" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="H57" s="22" t="inlineStr">
+      <c r="I57" s="22" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I57" s="22" t="inlineStr">
+      <c r="J57" s="22" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J57" s="22" t="inlineStr">
+      <c r="K57" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K57" s="22" t="inlineStr"/>
-      <c r="L57" s="23" t="inlineStr"/>
-      <c r="M57" s="22" t="inlineStr">
+      <c r="L57" s="22" t="inlineStr"/>
+      <c r="M57" s="24" t="inlineStr"/>
+      <c r="N57" s="23" t="inlineStr">
         <is>
           <t>info@azautoshop.com / you@email.com</t>
         </is>
       </c>
-      <c r="N57" s="24" t="inlineStr">
+      <c r="O57" s="25" t="inlineStr">
         <is>
           <t>Site excelente</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="25" t="n">
+      <c r="A58" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B58" s="26" t="inlineStr">
+      <c r="B58" s="27" t="inlineStr">
         <is>
           <t>Descartar</t>
         </is>
       </c>
-      <c r="C58" s="26" t="inlineStr">
+      <c r="C58" s="27" t="inlineStr">
         <is>
           <t>Unlimited Car Washes</t>
         </is>
       </c>
-      <c r="D58" s="26" t="inlineStr">
+      <c r="D58" s="27" t="inlineStr">
         <is>
           <t>car wash</t>
         </is>
       </c>
-      <c r="E58" s="26" t="inlineStr">
+      <c r="E58" s="27" t="inlineStr">
         <is>
           <t>Phoenix, AZ</t>
         </is>
       </c>
-      <c r="F58" s="26" t="inlineStr">
+      <c r="F58" s="28" t="inlineStr">
         <is>
           <t>superstarcarwashaz.com</t>
         </is>
       </c>
-      <c r="G58" s="25" t="n">
+      <c r="G58" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H58" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="H58" s="26" t="inlineStr">
+      <c r="I58" s="27" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I58" s="26" t="inlineStr">
+      <c r="J58" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J58" s="26" t="inlineStr">
+      <c r="K58" s="27" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="K58" s="26" t="inlineStr">
+      <c r="L58" s="28" t="inlineStr">
         <is>
           <t>@superstarcarwashes</t>
         </is>
       </c>
-      <c r="L58" s="27" t="n">
+      <c r="M58" s="29" t="n">
         <v>17000</v>
       </c>
-      <c r="M58" s="26" t="inlineStr"/>
-      <c r="N58" s="28" t="inlineStr">
+      <c r="N58" s="27" t="inlineStr"/>
+      <c r="O58" s="30" t="inlineStr">
         <is>
           <t>Rede grande AZ, IG 17K</t>
         </is>
@@ -5181,103 +5469,113 @@
           <t>Phoenix, AZ</t>
         </is>
       </c>
-      <c r="F59" s="22" t="inlineStr">
+      <c r="F59" s="23" t="inlineStr">
         <is>
           <t>tidycasa.com</t>
         </is>
       </c>
-      <c r="G59" s="21" t="n">
+      <c r="G59" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H59" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="H59" s="22" t="inlineStr">
+      <c r="I59" s="22" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I59" s="22" t="inlineStr">
+      <c r="J59" s="22" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J59" s="22" t="inlineStr">
+      <c r="K59" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K59" s="22" t="inlineStr"/>
-      <c r="L59" s="23" t="inlineStr"/>
-      <c r="M59" s="22" t="inlineStr">
+      <c r="L59" s="22" t="inlineStr"/>
+      <c r="M59" s="24" t="inlineStr"/>
+      <c r="N59" s="23" t="inlineStr">
         <is>
           <t>support@tidycasa.com</t>
         </is>
       </c>
-      <c r="N59" s="24" t="inlineStr">
+      <c r="O59" s="25" t="inlineStr">
         <is>
           <t>Moderno com booking 60s</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="25" t="n">
+      <c r="A60" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B60" s="26" t="inlineStr">
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>Descartar</t>
         </is>
       </c>
-      <c r="C60" s="26" t="inlineStr">
+      <c r="C60" s="27" t="inlineStr">
         <is>
           <t>Mobile Detailing Expert</t>
         </is>
       </c>
-      <c r="D60" s="26" t="inlineStr">
+      <c r="D60" s="27" t="inlineStr">
         <is>
           <t>detailing</t>
         </is>
       </c>
-      <c r="E60" s="26" t="inlineStr">
+      <c r="E60" s="27" t="inlineStr">
         <is>
           <t>Columbus, OH</t>
         </is>
       </c>
-      <c r="F60" s="26" t="inlineStr">
+      <c r="F60" s="28" t="inlineStr">
         <is>
           <t>mobiledetailingexpert.com</t>
         </is>
       </c>
-      <c r="G60" s="25" t="n">
+      <c r="G60" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H60" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="H60" s="26" t="inlineStr">
+      <c r="I60" s="27" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I60" s="26" t="inlineStr">
+      <c r="J60" s="27" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J60" s="26" t="inlineStr">
+      <c r="K60" s="27" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K60" s="26" t="inlineStr">
+      <c r="L60" s="28" t="inlineStr">
         <is>
           <t>@Mobiledetailingexpert</t>
         </is>
       </c>
-      <c r="L60" s="27" t="n">
+      <c r="M60" s="29" t="n">
         <v>765</v>
       </c>
-      <c r="M60" s="26" t="inlineStr">
+      <c r="N60" s="28" t="inlineStr">
         <is>
           <t>info@mobiledetailingexpert.com</t>
         </is>
       </c>
-      <c r="N60" s="28" t="inlineStr">
+      <c r="O60" s="30" t="inlineStr">
         <is>
           <t>Plataforma 80+ cidades, nao local</t>
         </is>
@@ -5307,93 +5605,103 @@
           <t>Columbus, OH</t>
         </is>
       </c>
-      <c r="F61" s="22" t="inlineStr">
+      <c r="F61" s="23" t="inlineStr">
         <is>
           <t>lucasdetailingcolumbus.com</t>
         </is>
       </c>
-      <c r="G61" s="21" t="n">
+      <c r="G61" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H61" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="H61" s="22" t="inlineStr">
+      <c r="I61" s="22" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I61" s="22" t="inlineStr">
+      <c r="J61" s="22" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J61" s="22" t="inlineStr">
+      <c r="K61" s="22" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="K61" s="22" t="inlineStr"/>
-      <c r="L61" s="23" t="inlineStr"/>
-      <c r="M61" s="22" t="inlineStr">
+      <c r="L61" s="22" t="inlineStr"/>
+      <c r="M61" s="24" t="inlineStr"/>
+      <c r="N61" s="23" t="inlineStr">
         <is>
           <t>info@lucasdetailingcolumbus.com</t>
         </is>
       </c>
-      <c r="N61" s="24" t="inlineStr">
+      <c r="O61" s="25" t="inlineStr">
         <is>
           <t>Moderno bonito</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="25" t="n">
+      <c r="A62" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B62" s="26" t="inlineStr">
+      <c r="B62" s="27" t="inlineStr">
         <is>
           <t>Descartar</t>
         </is>
       </c>
-      <c r="C62" s="26" t="inlineStr">
+      <c r="C62" s="27" t="inlineStr">
         <is>
           <t>Heating &amp; Air Conditioning Company Boise</t>
         </is>
       </c>
-      <c r="D62" s="26" t="inlineStr">
+      <c r="D62" s="27" t="inlineStr">
         <is>
           <t>hvac</t>
         </is>
       </c>
-      <c r="E62" s="26" t="inlineStr">
+      <c r="E62" s="27" t="inlineStr">
         <is>
           <t>Boise, ID</t>
         </is>
       </c>
-      <c r="F62" s="26" t="inlineStr">
+      <c r="F62" s="28" t="inlineStr">
         <is>
           <t>callpeppy.com</t>
         </is>
       </c>
-      <c r="G62" s="25" t="n">
+      <c r="G62" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H62" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="H62" s="26" t="inlineStr">
+      <c r="I62" s="27" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I62" s="26" t="inlineStr">
+      <c r="J62" s="27" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J62" s="26" t="inlineStr"/>
-      <c r="K62" s="26" t="inlineStr">
+      <c r="K62" s="27" t="inlineStr"/>
+      <c r="L62" s="28" t="inlineStr">
         <is>
           <t>@peppyheatingcooling</t>
         </is>
       </c>
-      <c r="L62" s="27" t="inlineStr"/>
-      <c r="M62" s="26" t="inlineStr"/>
-      <c r="N62" s="28" t="inlineStr">
+      <c r="M62" s="29" t="inlineStr"/>
+      <c r="N62" s="27" t="inlineStr"/>
+      <c r="O62" s="30" t="inlineStr">
         <is>
           <t>Branding forte com mascote</t>
         </is>
@@ -5423,101 +5731,111 @@
           <t>Jacksonville, FL</t>
         </is>
       </c>
-      <c r="F63" s="22" t="inlineStr">
+      <c r="F63" s="23" t="inlineStr">
         <is>
           <t>fairwaylawns.com</t>
         </is>
       </c>
-      <c r="G63" s="21" t="n">
+      <c r="G63" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H63" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="H63" s="22" t="inlineStr">
+      <c r="I63" s="22" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I63" s="22" t="inlineStr">
+      <c r="J63" s="22" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J63" s="22" t="inlineStr">
+      <c r="K63" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K63" s="22" t="inlineStr">
+      <c r="L63" s="23" t="inlineStr">
         <is>
           <t>@fairwaylawns</t>
         </is>
       </c>
-      <c r="L63" s="23" t="n">
+      <c r="M63" s="24" t="n">
         <v>1642</v>
       </c>
-      <c r="M63" s="22" t="inlineStr"/>
-      <c r="N63" s="24" t="inlineStr">
+      <c r="N63" s="22" t="inlineStr"/>
+      <c r="O63" s="25" t="inlineStr">
         <is>
           <t>Rede multi-estado, 78k reviews</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="25" t="n">
+      <c r="A64" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B64" s="26" t="inlineStr">
+      <c r="B64" s="27" t="inlineStr">
         <is>
           <t>Descartar</t>
         </is>
       </c>
-      <c r="C64" s="26" t="inlineStr">
+      <c r="C64" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">Natural Nail Salon &amp; Beauty Boutique in </t>
         </is>
       </c>
-      <c r="D64" s="26" t="inlineStr">
+      <c r="D64" s="27" t="inlineStr">
         <is>
           <t>nail salon</t>
         </is>
       </c>
-      <c r="E64" s="26" t="inlineStr">
+      <c r="E64" s="27" t="inlineStr">
         <is>
           <t>Nashville, TN</t>
         </is>
       </c>
-      <c r="F64" s="26" t="inlineStr">
+      <c r="F64" s="28" t="inlineStr">
         <is>
           <t>poppyandmonroe.com</t>
         </is>
       </c>
-      <c r="G64" s="25" t="n">
+      <c r="G64" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H64" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="H64" s="26" t="inlineStr">
+      <c r="I64" s="27" t="inlineStr">
         <is>
           <t>Squarespace</t>
         </is>
       </c>
-      <c r="I64" s="26" t="inlineStr">
+      <c r="J64" s="27" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J64" s="26" t="inlineStr"/>
-      <c r="K64" s="26" t="inlineStr">
+      <c r="K64" s="27" t="inlineStr"/>
+      <c r="L64" s="28" t="inlineStr">
         <is>
           <t>@poppyandmonroe</t>
         </is>
       </c>
-      <c r="L64" s="27" t="n">
+      <c r="M64" s="29" t="n">
         <v>17000</v>
       </c>
-      <c r="M64" s="26" t="inlineStr">
+      <c r="N64" s="28" t="inlineStr">
         <is>
           <t>hello@poppyandmonroe.com</t>
         </is>
       </c>
-      <c r="N64" s="28" t="inlineStr">
+      <c r="O64" s="30" t="inlineStr">
         <is>
           <t>Squarespace minimal chique</t>
         </is>
@@ -5547,91 +5865,101 @@
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="F65" s="22" t="inlineStr">
+      <c r="F65" s="23" t="inlineStr">
         <is>
           <t>zoomingroomin.com</t>
         </is>
       </c>
-      <c r="G65" s="21" t="n">
+      <c r="G65" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H65" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="H65" s="22" t="inlineStr">
+      <c r="I65" s="22" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I65" s="22" t="inlineStr">
+      <c r="J65" s="22" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J65" s="22" t="inlineStr"/>
       <c r="K65" s="22" t="inlineStr"/>
-      <c r="L65" s="23" t="inlineStr"/>
-      <c r="M65" s="22" t="inlineStr"/>
-      <c r="N65" s="24" t="inlineStr">
+      <c r="L65" s="22" t="inlineStr"/>
+      <c r="M65" s="24" t="inlineStr"/>
+      <c r="N65" s="22" t="inlineStr"/>
+      <c r="O65" s="25" t="inlineStr">
         <is>
           <t>Moderno; escala nacional</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="25" t="n">
+      <c r="A66" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B66" s="26" t="inlineStr">
+      <c r="B66" s="27" t="inlineStr">
         <is>
           <t>Descartar</t>
         </is>
       </c>
-      <c r="C66" s="26" t="inlineStr">
+      <c r="C66" s="27" t="inlineStr">
         <is>
           <t>Nashville Roofing Company</t>
         </is>
       </c>
-      <c r="D66" s="26" t="inlineStr">
+      <c r="D66" s="27" t="inlineStr">
         <is>
           <t>roofing</t>
         </is>
       </c>
-      <c r="E66" s="26" t="inlineStr">
+      <c r="E66" s="27" t="inlineStr">
         <is>
           <t>Nashville, TN</t>
         </is>
       </c>
-      <c r="F66" s="26" t="inlineStr">
+      <c r="F66" s="28" t="inlineStr">
         <is>
           <t>billraganroofing.com</t>
         </is>
       </c>
-      <c r="G66" s="25" t="n">
+      <c r="G66" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H66" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="H66" s="26" t="inlineStr">
+      <c r="I66" s="27" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I66" s="26" t="inlineStr">
+      <c r="J66" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J66" s="26" t="inlineStr">
+      <c r="K66" s="27" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K66" s="26" t="inlineStr">
+      <c r="L66" s="28" t="inlineStr">
         <is>
           <t>@billraganroofing</t>
         </is>
       </c>
-      <c r="L66" s="27" t="n">
+      <c r="M66" s="29" t="n">
         <v>482</v>
       </c>
-      <c r="M66" s="26" t="inlineStr"/>
-      <c r="N66" s="28" t="inlineStr">
+      <c r="N66" s="27" t="inlineStr"/>
+      <c r="O66" s="30" t="inlineStr">
         <is>
           <t>Site forte estilo HubSpot com calculadora</t>
         </is>
@@ -5661,105 +5989,115 @@
           <t>Nashville, TN</t>
         </is>
       </c>
-      <c r="F67" s="22" t="inlineStr">
+      <c r="F67" s="23" t="inlineStr">
         <is>
           <t>nashvilleroofingco.com</t>
         </is>
       </c>
-      <c r="G67" s="21" t="n">
+      <c r="G67" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H67" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="H67" s="22" t="inlineStr">
+      <c r="I67" s="22" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I67" s="22" t="inlineStr">
+      <c r="J67" s="22" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J67" s="22" t="inlineStr">
+      <c r="K67" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K67" s="22" t="inlineStr">
+      <c r="L67" s="23" t="inlineStr">
         <is>
           <t>@nashroofingco</t>
         </is>
       </c>
-      <c r="L67" s="23" t="n">
+      <c r="M67" s="24" t="n">
         <v>694</v>
       </c>
-      <c r="M67" s="22" t="inlineStr">
+      <c r="N67" s="23" t="inlineStr">
         <is>
           <t>info@nashvilleroofingco.com</t>
         </is>
       </c>
-      <c r="N67" s="24" t="inlineStr">
+      <c r="O67" s="25" t="inlineStr">
         <is>
           <t>Moderno forte</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="25" t="n">
+      <c r="A68" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B68" s="26" t="inlineStr">
+      <c r="B68" s="27" t="inlineStr">
         <is>
           <t>Descartar</t>
         </is>
       </c>
-      <c r="C68" s="26" t="inlineStr">
+      <c r="C68" s="27" t="inlineStr">
         <is>
           <t>Ultrashade Tattoos</t>
         </is>
       </c>
-      <c r="D68" s="26" t="inlineStr">
+      <c r="D68" s="27" t="inlineStr">
         <is>
           <t>tattoo</t>
         </is>
       </c>
-      <c r="E68" s="26" t="inlineStr">
+      <c r="E68" s="27" t="inlineStr">
         <is>
           <t>Columbus, OH</t>
         </is>
       </c>
-      <c r="F68" s="26" t="inlineStr">
+      <c r="F68" s="28" t="inlineStr">
         <is>
           <t>ultrashadetattoos.com</t>
         </is>
       </c>
-      <c r="G68" s="25" t="n">
+      <c r="G68" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H68" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="H68" s="26" t="inlineStr">
+      <c r="I68" s="27" t="inlineStr">
         <is>
           <t>Squarespace</t>
         </is>
       </c>
-      <c r="I68" s="26" t="inlineStr">
+      <c r="J68" s="27" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
-      <c r="J68" s="26" t="inlineStr"/>
-      <c r="K68" s="26" t="inlineStr">
+      <c r="K68" s="27" t="inlineStr"/>
+      <c r="L68" s="28" t="inlineStr">
         <is>
           <t>@ultrashadetattoos</t>
         </is>
       </c>
-      <c r="L68" s="27" t="n">
+      <c r="M68" s="29" t="n">
         <v>6756</v>
       </c>
-      <c r="M68" s="26" t="inlineStr">
+      <c r="N68" s="28" t="inlineStr">
         <is>
           <t>ultrashadetattoos@gmail.com</t>
         </is>
       </c>
-      <c r="N68" s="28" t="inlineStr">
+      <c r="O68" s="30" t="inlineStr">
         <is>
           <t>Site premium chique</t>
         </is>
@@ -5789,104 +6127,114 @@
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="F69" s="22" t="inlineStr">
+      <c r="F69" s="23" t="inlineStr">
         <is>
           <t>tidalwaveautospa.com</t>
         </is>
       </c>
-      <c r="G69" s="21" t="n">
+      <c r="G69" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H69" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="H69" s="22" t="inlineStr">
+      <c r="I69" s="22" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I69" s="22" t="inlineStr">
+      <c r="J69" s="22" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J69" s="22" t="inlineStr">
+      <c r="K69" s="22" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K69" s="22" t="inlineStr">
+      <c r="L69" s="23" t="inlineStr">
         <is>
           <t>@tidalwaveautospa</t>
         </is>
       </c>
-      <c r="L69" s="23" t="n">
+      <c r="M69" s="24" t="n">
         <v>4431</v>
       </c>
-      <c r="M69" s="22" t="inlineStr"/>
-      <c r="N69" s="24" t="inlineStr">
+      <c r="N69" s="22" t="inlineStr"/>
+      <c r="O69" s="25" t="inlineStr">
         <is>
           <t>Corporacao 200+ unidades</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="25" t="n">
+      <c r="A70" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="B70" s="26" t="inlineStr">
+      <c r="B70" s="27" t="inlineStr">
         <is>
           <t>Descartar</t>
         </is>
       </c>
-      <c r="C70" s="26" t="inlineStr">
+      <c r="C70" s="27" t="inlineStr">
         <is>
           <t>Autobell® Car Wash</t>
         </is>
       </c>
-      <c r="D70" s="26" t="inlineStr">
+      <c r="D70" s="27" t="inlineStr">
         <is>
           <t>car wash</t>
         </is>
       </c>
-      <c r="E70" s="26" t="inlineStr">
+      <c r="E70" s="27" t="inlineStr">
         <is>
           <t>Charlotte, NC</t>
         </is>
       </c>
-      <c r="F70" s="26" t="inlineStr">
+      <c r="F70" s="28" t="inlineStr">
         <is>
           <t>autobell.com</t>
         </is>
       </c>
-      <c r="G70" s="25" t="n">
+      <c r="G70" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="H70" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="H70" s="26" t="inlineStr">
+      <c r="I70" s="27" t="inlineStr">
         <is>
           <t>sob medida</t>
         </is>
       </c>
-      <c r="I70" s="26" t="inlineStr">
+      <c r="J70" s="27" t="inlineStr">
         <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J70" s="26" t="inlineStr"/>
-      <c r="K70" s="26" t="inlineStr">
+      <c r="K70" s="27" t="inlineStr"/>
+      <c r="L70" s="28" t="inlineStr">
         <is>
           <t>@AutoBellCarWash</t>
         </is>
       </c>
-      <c r="L70" s="27" t="n">
+      <c r="M70" s="29" t="n">
         <v>6132</v>
       </c>
-      <c r="M70" s="26" t="inlineStr"/>
-      <c r="N70" s="28" t="inlineStr">
+      <c r="N70" s="27" t="inlineStr"/>
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>Corporacao 75+ unidades</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N70"/>
+  <autoFilter ref="A4:O70"/>
   <conditionalFormatting sqref="A5:A70">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>8</formula>
@@ -5899,7 +6247,7 @@
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G70">
+  <conditionalFormatting sqref="H5:H70">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -5908,7 +6256,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L5:L70">
+  <conditionalFormatting sqref="M5:M70">
     <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="min"/>
@@ -5917,6 +6265,226 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId218"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5927,7 +6495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5935,15 +6503,16 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="58" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="58" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -5983,50 +6552,55 @@
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>Site</t>
+          <t>Site (clique)</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Print do site</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
+          <t>Instagram (clique)</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
           <t>Seguidores</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
-        <is>
-          <t>E-mail</t>
-        </is>
-      </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
+          <t>E-mail (clique)</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
           <t>Ângulo de abordagem</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K4" s="10" t="inlineStr">
+      <c r="L4" s="10" t="inlineStr">
         <is>
           <t>Seguiu em</t>
         </is>
       </c>
-      <c r="L4" s="10" t="inlineStr">
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>Comentou em</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>DM enviada em</t>
         </is>
       </c>
-      <c r="N4" s="10" t="inlineStr">
+      <c r="O4" s="10" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -6051,70 +6625,80 @@
           <t>Columbus, OH</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>macronmobile.com</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr"/>
-      <c r="G5" s="23" t="inlineStr"/>
-      <c r="H5" s="22" t="inlineStr"/>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr"/>
+      <c r="H5" s="24" t="inlineStr"/>
+      <c r="I5" s="22" t="inlineStr"/>
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>Site de 2013 com botoes bisotados; detailing premium (pacotes de USD 350) = tem caixa; redesign completo + booking</t>
         </is>
       </c>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K5" s="29" t="inlineStr"/>
-      <c r="L5" s="29" t="inlineStr"/>
-      <c r="M5" s="29" t="inlineStr"/>
-      <c r="N5" s="24" t="inlineStr"/>
+      <c r="L5" s="31" t="inlineStr"/>
+      <c r="M5" s="31" t="inlineStr"/>
+      <c r="N5" s="31" t="inlineStr"/>
+      <c r="O5" s="25" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="n">
+      <c r="A6" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>Octopus Car Washes in Florida</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>car wash</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>octopuscarwashflorida.com</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr"/>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
       <c r="G6" s="27" t="inlineStr"/>
-      <c r="H6" s="26" t="inlineStr"/>
-      <c r="I6" s="26" t="inlineStr">
+      <c r="H6" s="29" t="inlineStr"/>
+      <c r="I6" s="27" t="inlineStr"/>
+      <c r="J6" s="27" t="inlineStr">
         <is>
           <t>Layout anos 2000, logo clipart, fundo de bolhas; 2 unidades familiares; redesign + booking</t>
         </is>
       </c>
-      <c r="J6" s="26" t="inlineStr">
+      <c r="K6" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K6" s="30" t="inlineStr"/>
-      <c r="L6" s="30" t="inlineStr"/>
-      <c r="M6" s="30" t="inlineStr"/>
-      <c r="N6" s="28" t="inlineStr"/>
+      <c r="L6" s="32" t="inlineStr"/>
+      <c r="M6" s="32" t="inlineStr"/>
+      <c r="N6" s="32" t="inlineStr"/>
+      <c r="O6" s="30" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="21" t="n">
@@ -6135,80 +6719,90 @@
           <t>Phoenix, AZ</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>pvcarwash.com</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr"/>
-      <c r="G7" s="23" t="inlineStr"/>
-      <c r="H7" s="22" t="inlineStr"/>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr"/>
+      <c r="H7" s="24" t="inlineStr"/>
+      <c r="I7" s="22" t="inlineStr"/>
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>Template generico ~2010, 1 unidade + loja de conveniencia; redesign completo</t>
         </is>
       </c>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K7" s="29" t="inlineStr"/>
-      <c r="L7" s="29" t="inlineStr"/>
-      <c r="M7" s="29" t="inlineStr"/>
-      <c r="N7" s="24" t="inlineStr"/>
+      <c r="L7" s="31" t="inlineStr"/>
+      <c r="M7" s="31" t="inlineStr"/>
+      <c r="N7" s="31" t="inlineStr"/>
+      <c r="O7" s="25" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="n">
+      <c r="A8" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Curbside Mobile Detailing®</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>detailing</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Columbus, OH</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>curbsidemobiledetailing.com</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t>@curbsidemobiledetailing</t>
         </is>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="H8" s="29" t="n">
         <v>1583</v>
       </c>
-      <c r="H8" s="26" t="inlineStr">
+      <c r="I8" s="28" t="inlineStr">
         <is>
           <t>info@curbsidemobiledetailing.com</t>
         </is>
       </c>
-      <c r="I8" s="26" t="inlineStr">
+      <c r="J8" s="27" t="inlineStr">
         <is>
           <t>No ar desde 2001, layout 2012, embed YouTube antigo; historia forte pra contar num site novo</t>
         </is>
       </c>
-      <c r="J8" s="26" t="inlineStr">
+      <c r="K8" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K8" s="30" t="inlineStr"/>
-      <c r="L8" s="30" t="inlineStr"/>
-      <c r="M8" s="30" t="inlineStr"/>
-      <c r="N8" s="28" t="inlineStr"/>
+      <c r="L8" s="32" t="inlineStr"/>
+      <c r="M8" s="32" t="inlineStr"/>
+      <c r="N8" s="32" t="inlineStr"/>
+      <c r="O8" s="30" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="21" t="n">
@@ -6229,84 +6823,94 @@
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>championshipmartialarts.com</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr"/>
-      <c r="G9" s="23" t="inlineStr"/>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr"/>
+      <c r="H9" s="24" t="inlineStr"/>
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>p.paquet@d-a-m.ca / holsej@pakskarate.com / capecoral@randori-pro.com</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>Hero quebrado (secao em branco, form solto); multi-unidades em Orlando; consertar = venda facil de mostrar</t>
         </is>
       </c>
-      <c r="J9" s="22" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K9" s="29" t="inlineStr"/>
-      <c r="L9" s="29" t="inlineStr"/>
-      <c r="M9" s="29" t="inlineStr"/>
-      <c r="N9" s="24" t="inlineStr"/>
+      <c r="L9" s="31" t="inlineStr"/>
+      <c r="M9" s="31" t="inlineStr"/>
+      <c r="N9" s="31" t="inlineStr"/>
+      <c r="O9" s="25" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="n">
+      <c r="A10" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>ᐅ #1 Mobile Pet Grooming in Doral, Flori</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>pet grooming</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>purrfectgrooming.pet</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr">
         <is>
           <t>@purrfectgrooming.pet</t>
         </is>
       </c>
-      <c r="G10" s="27" t="n">
+      <c r="H10" s="29" t="n">
         <v>4980</v>
       </c>
-      <c r="H10" s="26" t="inlineStr">
+      <c r="I10" s="28" t="inlineStr">
         <is>
           <t>contactus@purrfectgrooming.pet</t>
         </is>
       </c>
-      <c r="I10" s="26" t="inlineStr">
+      <c r="J10" s="27" t="inlineStr">
         <is>
           <t>Hero quebrado com sobreposicao de logo; frota adesivada (investe em marca); ATENCAO: sede em Doral/Miami</t>
         </is>
       </c>
-      <c r="J10" s="26" t="inlineStr">
+      <c r="K10" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K10" s="30" t="inlineStr"/>
-      <c r="L10" s="30" t="inlineStr"/>
-      <c r="M10" s="30" t="inlineStr"/>
-      <c r="N10" s="28" t="inlineStr"/>
+      <c r="L10" s="32" t="inlineStr"/>
+      <c r="M10" s="32" t="inlineStr"/>
+      <c r="N10" s="32" t="inlineStr"/>
+      <c r="O10" s="30" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="21" t="n">
@@ -6327,74 +6931,84 @@
           <t>Kansas City, MO</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>choicetreeservicekc.com</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr"/>
-      <c r="G11" s="23" t="inlineStr"/>
-      <c r="H11" s="22" t="inlineStr"/>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr"/>
+      <c r="H11" s="24" t="inlineStr"/>
+      <c r="I11" s="22" t="inlineStr"/>
+      <c r="J11" s="22" t="inlineStr">
         <is>
           <t>Copyright 2011, template bootstrap velho, form denso; negocio real com 2 telefones</t>
         </is>
       </c>
-      <c r="J11" s="22" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K11" s="29" t="inlineStr"/>
-      <c r="L11" s="29" t="inlineStr"/>
-      <c r="M11" s="29" t="inlineStr"/>
-      <c r="N11" s="24" t="inlineStr"/>
+      <c r="L11" s="31" t="inlineStr"/>
+      <c r="M11" s="31" t="inlineStr"/>
+      <c r="N11" s="31" t="inlineStr"/>
+      <c r="O11" s="25" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="n">
+      <c r="A12" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>Phoenix Auto Repair</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>auto repair</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Phoenix, AZ</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>phoenixautoshop.com</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr"/>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
       <c r="G12" s="27" t="inlineStr"/>
-      <c r="H12" s="26" t="inlineStr">
+      <c r="H12" s="29" t="inlineStr"/>
+      <c r="I12" s="28" t="inlineStr">
         <is>
           <t>mickey@phoenixautoshop.com</t>
         </is>
       </c>
-      <c r="I12" s="26" t="inlineStr">
+      <c r="J12" s="27" t="inlineStr">
         <is>
           <t>Divi roxo datado ~2015; oficina familiar desde 1979; email do dono (mickey@) exposto no site</t>
         </is>
       </c>
-      <c r="J12" s="26" t="inlineStr">
+      <c r="K12" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K12" s="30" t="inlineStr"/>
-      <c r="L12" s="30" t="inlineStr"/>
-      <c r="M12" s="30" t="inlineStr"/>
-      <c r="N12" s="28" t="inlineStr"/>
+      <c r="L12" s="32" t="inlineStr"/>
+      <c r="M12" s="32" t="inlineStr"/>
+      <c r="N12" s="32" t="inlineStr"/>
+      <c r="O12" s="30" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="21" t="n">
@@ -6415,70 +7029,80 @@
           <t>Phoenix, AZ</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>touchlesscarwash.com</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr"/>
-      <c r="G13" s="23" t="inlineStr"/>
-      <c r="H13" s="22" t="inlineStr"/>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr"/>
+      <c r="H13" s="24" t="inlineStr"/>
+      <c r="I13" s="22" t="inlineStr"/>
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>Visual datado, video com texto arial; rede local pequena de Phoenix</t>
         </is>
       </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K13" s="29" t="inlineStr"/>
-      <c r="L13" s="29" t="inlineStr"/>
-      <c r="M13" s="29" t="inlineStr"/>
-      <c r="N13" s="24" t="inlineStr"/>
+      <c r="L13" s="31" t="inlineStr"/>
+      <c r="M13" s="31" t="inlineStr"/>
+      <c r="N13" s="31" t="inlineStr"/>
+      <c r="O13" s="25" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="n">
+      <c r="A14" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>San Antonio Fence Company</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>fencing</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>sanantoniofencecompany.net</t>
         </is>
       </c>
-      <c r="F14" s="26" t="inlineStr"/>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
       <c r="G14" s="27" t="inlineStr"/>
-      <c r="H14" s="26" t="inlineStr"/>
-      <c r="I14" s="26" t="inlineStr">
+      <c r="H14" s="29" t="inlineStr"/>
+      <c r="I14" s="27" t="inlineStr"/>
+      <c r="J14" s="27" t="inlineStr">
         <is>
           <t>Weebly DIY, tipografia generica, fotos reais; dono fez sozinho</t>
         </is>
       </c>
-      <c r="J14" s="26" t="inlineStr">
+      <c r="K14" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K14" s="30" t="inlineStr"/>
-      <c r="L14" s="30" t="inlineStr"/>
-      <c r="M14" s="30" t="inlineStr"/>
-      <c r="N14" s="28" t="inlineStr"/>
+      <c r="L14" s="32" t="inlineStr"/>
+      <c r="M14" s="32" t="inlineStr"/>
+      <c r="N14" s="32" t="inlineStr"/>
+      <c r="O14" s="30" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="21" t="n">
@@ -6499,84 +7123,94 @@
           <t>Boise, ID</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>westernhvac.com</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>@westernhvac</t>
         </is>
       </c>
-      <c r="G15" s="23" t="n">
+      <c r="H15" s="24" t="n">
         <v>2281</v>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>csr@westernhvac.com / tom@westernhvac.com / max@westernhvac.com</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>Logo 3D anos 2000, botoes de ticket; desde 1967, Carrier dealer = caixa; decisao pode ser lenta</t>
         </is>
       </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K15" s="29" t="inlineStr"/>
-      <c r="L15" s="29" t="inlineStr"/>
-      <c r="M15" s="29" t="inlineStr"/>
-      <c r="N15" s="24" t="inlineStr"/>
+      <c r="L15" s="31" t="inlineStr"/>
+      <c r="M15" s="31" t="inlineStr"/>
+      <c r="N15" s="31" t="inlineStr"/>
+      <c r="O15" s="25" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="n">
+      <c r="A16" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>Landscape Company</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>landscaping</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Columbus, OH</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>sciotolandscaping.com</t>
         </is>
       </c>
-      <c r="F16" s="26" t="inlineStr"/>
+      <c r="F16" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
       <c r="G16" s="27" t="inlineStr"/>
-      <c r="H16" s="26" t="inlineStr">
+      <c r="H16" s="29" t="inlineStr"/>
+      <c r="I16" s="28" t="inlineStr">
         <is>
           <t>info@sciotolandscaping.com</t>
         </is>
       </c>
-      <c r="I16" s="26" t="inlineStr">
+      <c r="J16" s="27" t="inlineStr">
         <is>
           <t>Template 2012 com foto de banco de imagem; info@ visivel no header</t>
         </is>
       </c>
-      <c r="J16" s="26" t="inlineStr">
+      <c r="K16" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K16" s="30" t="inlineStr"/>
-      <c r="L16" s="30" t="inlineStr"/>
-      <c r="M16" s="30" t="inlineStr"/>
-      <c r="N16" s="28" t="inlineStr"/>
+      <c r="L16" s="32" t="inlineStr"/>
+      <c r="M16" s="32" t="inlineStr"/>
+      <c r="N16" s="32" t="inlineStr"/>
+      <c r="O16" s="30" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="21" t="n">
@@ -6597,84 +7231,94 @@
           <t>Charlotte, NC</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>straightedgepaintingpros.com</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr"/>
-      <c r="G17" s="23" t="inlineStr"/>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr"/>
+      <c r="H17" s="24" t="inlineStr"/>
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>straightedgepp@gmail.com</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="J17" s="22" t="inlineStr">
         <is>
           <t>Logo clipart, WP basico; 49 reviews 4.8 = negocio bom com site fraco</t>
         </is>
       </c>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="K17" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K17" s="29" t="inlineStr"/>
-      <c r="L17" s="29" t="inlineStr"/>
-      <c r="M17" s="29" t="inlineStr"/>
-      <c r="N17" s="24" t="inlineStr"/>
+      <c r="L17" s="31" t="inlineStr"/>
+      <c r="M17" s="31" t="inlineStr"/>
+      <c r="N17" s="31" t="inlineStr"/>
+      <c r="O17" s="25" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="n">
+      <c r="A18" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>All Creatures Pet Grooming</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>pet grooming</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>allcreaturespetgrooming.com</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="G18" s="28" t="inlineStr">
         <is>
           <t>@allcreaturespetgrooming</t>
         </is>
       </c>
-      <c r="G18" s="27" t="n">
+      <c r="H18" s="29" t="n">
         <v>3277</v>
       </c>
-      <c r="H18" s="26" t="inlineStr">
+      <c r="I18" s="28" t="inlineStr">
         <is>
           <t>info@allcreaturespetgrooming.com</t>
         </is>
       </c>
-      <c r="I18" s="26" t="inlineStr">
+      <c r="J18" s="27" t="inlineStr">
         <is>
           <t>Wix DIY com logo duplicado gigante e layout desalinhado; tem booking</t>
         </is>
       </c>
-      <c r="J18" s="26" t="inlineStr">
+      <c r="K18" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K18" s="30" t="inlineStr"/>
-      <c r="L18" s="30" t="inlineStr"/>
-      <c r="M18" s="30" t="inlineStr"/>
-      <c r="N18" s="28" t="inlineStr"/>
+      <c r="L18" s="32" t="inlineStr"/>
+      <c r="M18" s="32" t="inlineStr"/>
+      <c r="N18" s="32" t="inlineStr"/>
+      <c r="O18" s="30" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="21" t="n">
@@ -6695,80 +7339,90 @@
           <t>Kansas City, MO</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>bloombakingco.com</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>@bloombakingco</t>
         </is>
       </c>
-      <c r="G19" s="23" t="n">
+      <c r="H19" s="24" t="n">
         <v>4204</v>
       </c>
-      <c r="H19" s="22" t="inlineStr"/>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I19" s="22" t="inlineStr"/>
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>Layout ~2015 (Duda), logo simples; padaria artesanal com IG</t>
         </is>
       </c>
-      <c r="J19" s="22" t="inlineStr">
+      <c r="K19" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K19" s="29" t="inlineStr"/>
-      <c r="L19" s="29" t="inlineStr"/>
-      <c r="M19" s="29" t="inlineStr"/>
-      <c r="N19" s="24" t="inlineStr"/>
+      <c r="L19" s="31" t="inlineStr"/>
+      <c r="M19" s="31" t="inlineStr"/>
+      <c r="N19" s="31" t="inlineStr"/>
+      <c r="O19" s="25" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="n">
+      <c r="A20" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>Car wash in Tampa</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>car wash</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>Tampa, FL</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E20" s="28" t="inlineStr">
         <is>
           <t>bluswancarwashtampa.com</t>
         </is>
       </c>
-      <c r="F20" s="26" t="inlineStr"/>
+      <c r="F20" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
       <c r="G20" s="27" t="inlineStr"/>
-      <c r="H20" s="26" t="inlineStr">
+      <c r="H20" s="29" t="inlineStr"/>
+      <c r="I20" s="28" t="inlineStr">
         <is>
           <t>bluswancarwash@gmail.com</t>
         </is>
       </c>
-      <c r="I20" s="26" t="inlineStr">
+      <c r="J20" s="27" t="inlineStr">
         <is>
           <t>GoDaddy DIY, 1 unidade; template razoavel mas generico</t>
         </is>
       </c>
-      <c r="J20" s="26" t="inlineStr">
+      <c r="K20" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K20" s="30" t="inlineStr"/>
-      <c r="L20" s="30" t="inlineStr"/>
-      <c r="M20" s="30" t="inlineStr"/>
-      <c r="N20" s="28" t="inlineStr"/>
+      <c r="L20" s="32" t="inlineStr"/>
+      <c r="M20" s="32" t="inlineStr"/>
+      <c r="N20" s="32" t="inlineStr"/>
+      <c r="O20" s="30" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="21" t="n">
@@ -6789,84 +7443,94 @@
           <t>San Antonio, TX</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>alamofencesa.com</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>@alamofencesa</t>
         </is>
       </c>
-      <c r="G21" s="23" t="n">
+      <c r="H21" s="24" t="n">
         <v>88</v>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="I21" s="23" t="inlineStr">
         <is>
           <t>customerservice@alamofencesa.com</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="J21" s="22" t="inlineStr">
         <is>
           <t>Layout centrado antigo; customerservice@ exposto; negocio estabelecido</t>
         </is>
       </c>
-      <c r="J21" s="22" t="inlineStr">
+      <c r="K21" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K21" s="29" t="inlineStr"/>
-      <c r="L21" s="29" t="inlineStr"/>
-      <c r="M21" s="29" t="inlineStr"/>
-      <c r="N21" s="24" t="inlineStr"/>
+      <c r="L21" s="31" t="inlineStr"/>
+      <c r="M21" s="31" t="inlineStr"/>
+      <c r="N21" s="31" t="inlineStr"/>
+      <c r="O21" s="25" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="n">
+      <c r="A22" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="27" t="inlineStr">
         <is>
           <t>Boise HVAC</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
         <is>
           <t>hvac</t>
         </is>
       </c>
-      <c r="D22" s="26" t="inlineStr">
+      <c r="D22" s="27" t="inlineStr">
         <is>
           <t>Boise, ID</t>
         </is>
       </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="E22" s="28" t="inlineStr">
         <is>
           <t>ims365hvac.com</t>
         </is>
       </c>
-      <c r="F22" s="26" t="inlineStr"/>
+      <c r="F22" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
       <c r="G22" s="27" t="inlineStr"/>
-      <c r="H22" s="26" t="inlineStr">
+      <c r="H22" s="29" t="inlineStr"/>
+      <c r="I22" s="28" t="inlineStr">
         <is>
           <t>service@ims365hvac.com</t>
         </is>
       </c>
-      <c r="I22" s="26" t="inlineStr">
+      <c r="J22" s="27" t="inlineStr">
         <is>
           <t>WP generico, hero cru; empresa 25+ anos</t>
         </is>
       </c>
-      <c r="J22" s="26" t="inlineStr">
+      <c r="K22" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K22" s="30" t="inlineStr"/>
-      <c r="L22" s="30" t="inlineStr"/>
-      <c r="M22" s="30" t="inlineStr"/>
-      <c r="N22" s="28" t="inlineStr"/>
+      <c r="L22" s="32" t="inlineStr"/>
+      <c r="M22" s="32" t="inlineStr"/>
+      <c r="N22" s="32" t="inlineStr"/>
+      <c r="O22" s="30" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="21" t="n">
@@ -6887,90 +7551,100 @@
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>martialartsworldorlando.com</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
         <is>
           <t>@maworlando</t>
         </is>
       </c>
-      <c r="G23" s="23" t="n">
+      <c r="H23" s="24" t="n">
         <v>1049</v>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="I23" s="23" t="inlineStr">
         <is>
           <t>orlandoadmin@mawus.com</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="J23" s="22" t="inlineStr">
         <is>
           <t>Logo anos 90, layout mediano; academia local com programas</t>
         </is>
       </c>
-      <c r="J23" s="22" t="inlineStr">
+      <c r="K23" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K23" s="29" t="inlineStr"/>
-      <c r="L23" s="29" t="inlineStr"/>
-      <c r="M23" s="29" t="inlineStr"/>
-      <c r="N23" s="24" t="inlineStr"/>
+      <c r="L23" s="31" t="inlineStr"/>
+      <c r="M23" s="31" t="inlineStr"/>
+      <c r="N23" s="31" t="inlineStr"/>
+      <c r="O23" s="25" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="n">
+      <c r="A24" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>Power Wash Pro Plus</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C24" s="27" t="inlineStr">
         <is>
           <t>pressure washing</t>
         </is>
       </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="D24" s="27" t="inlineStr">
         <is>
           <t>Jacksonville, FL</t>
         </is>
       </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="E24" s="28" t="inlineStr">
         <is>
           <t>powerwashproplus.com</t>
         </is>
       </c>
-      <c r="F24" s="26" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="G24" s="28" t="inlineStr">
         <is>
           <t>@powerwashproplus</t>
         </is>
       </c>
-      <c r="G24" s="27" t="n">
+      <c r="H24" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="H24" s="26" t="inlineStr">
+      <c r="I24" s="28" t="inlineStr">
         <is>
           <t>powerwashproplus@gmail.com</t>
         </is>
       </c>
-      <c r="I24" s="26" t="inlineStr">
+      <c r="J24" s="27" t="inlineStr">
         <is>
           <t>Squarespace generico, logo clipart, hero fraco; facil mostrar upgrade</t>
         </is>
       </c>
-      <c r="J24" s="26" t="inlineStr">
+      <c r="K24" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K24" s="30" t="inlineStr"/>
-      <c r="L24" s="30" t="inlineStr"/>
-      <c r="M24" s="30" t="inlineStr"/>
-      <c r="N24" s="28" t="inlineStr"/>
+      <c r="L24" s="32" t="inlineStr"/>
+      <c r="M24" s="32" t="inlineStr"/>
+      <c r="N24" s="32" t="inlineStr"/>
+      <c r="O24" s="30" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="21" t="n">
@@ -6991,41 +7665,46 @@
           <t>Columbus, OH</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>tatsbywes.com</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>abrir print</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>@wes_tattoos_columbus</t>
         </is>
       </c>
-      <c r="G25" s="23" t="n">
+      <c r="H25" s="24" t="n">
         <v>11000</v>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="I25" s="23" t="inlineStr">
         <is>
           <t>tatsbywes97@gmail.com</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="J25" s="22" t="inlineStr">
         <is>
           <t>Artista solo desde 1997; site simples escuro; decisao rapida, IG e a vida do tatuador</t>
         </is>
       </c>
-      <c r="J25" s="22" t="inlineStr">
+      <c r="K25" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="K25" s="29" t="inlineStr"/>
-      <c r="L25" s="29" t="inlineStr"/>
-      <c r="M25" s="29" t="inlineStr"/>
-      <c r="N25" s="24" t="inlineStr"/>
+      <c r="L25" s="31" t="inlineStr"/>
+      <c r="M25" s="31" t="inlineStr"/>
+      <c r="N25" s="31" t="inlineStr"/>
+      <c r="O25" s="25" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N25"/>
+  <autoFilter ref="A4:O25"/>
   <conditionalFormatting sqref="A5:A25">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>8</formula>
@@ -7035,7 +7714,7 @@
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J25">
+  <conditionalFormatting sqref="K5:K25">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="3">
       <formula>"Ganho"</formula>
     </cfRule>
@@ -7047,10 +7726,77 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K5:K25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A fazer,Seguindo,Comentou,DM enviada,Respondeu,Prévia enviada,Negociando,Ganho,Perdido"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId65"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7137,12 +7883,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>@purrfectgrooming.pet</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="24" t="n">
         <v>4980</v>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -7158,53 +7904,53 @@
       <c r="E5" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>purrfectgrooming.pet</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr"/>
       <c r="H5" s="22" t="inlineStr"/>
-      <c r="I5" s="24" t="inlineStr"/>
+      <c r="I5" s="25" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>@curbsidemobiledetailing</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
+      <c r="B6" s="29" t="n">
         <v>1583</v>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>detailing</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Columbus, OH</t>
         </is>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>curbsidemobiledetailing.com</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr"/>
-      <c r="H6" s="26" t="inlineStr"/>
-      <c r="I6" s="28" t="inlineStr"/>
+      <c r="G6" s="27" t="inlineStr"/>
+      <c r="H6" s="27" t="inlineStr"/>
+      <c r="I6" s="30" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>@allcreaturespetgrooming</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B7" s="24" t="n">
         <v>3277</v>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -7220,53 +7966,53 @@
       <c r="E7" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>allcreaturespetgrooming.com</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr"/>
       <c r="H7" s="22" t="inlineStr"/>
-      <c r="I7" s="24" t="inlineStr"/>
+      <c r="I7" s="25" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>@westernhvac</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
+      <c r="B8" s="29" t="n">
         <v>2281</v>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>hvac</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Boise, ID</t>
         </is>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>westernhvac.com</t>
         </is>
       </c>
-      <c r="G8" s="26" t="inlineStr"/>
-      <c r="H8" s="26" t="inlineStr"/>
-      <c r="I8" s="28" t="inlineStr"/>
+      <c r="G8" s="27" t="inlineStr"/>
+      <c r="H8" s="27" t="inlineStr"/>
+      <c r="I8" s="30" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>@wes_tattoos_columbus</t>
         </is>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="24" t="n">
         <v>11000</v>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -7282,53 +8028,53 @@
       <c r="E9" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>tatsbywes.com</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr"/>
       <c r="H9" s="22" t="inlineStr"/>
-      <c r="I9" s="24" t="inlineStr"/>
+      <c r="I9" s="25" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>@bloombakingco</t>
         </is>
       </c>
-      <c r="B10" s="27" t="n">
+      <c r="B10" s="29" t="n">
         <v>4204</v>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>bakery</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Kansas City, MO</t>
         </is>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>bloombakingco.com</t>
         </is>
       </c>
-      <c r="G10" s="26" t="inlineStr"/>
-      <c r="H10" s="26" t="inlineStr"/>
-      <c r="I10" s="28" t="inlineStr"/>
+      <c r="G10" s="27" t="inlineStr"/>
+      <c r="H10" s="27" t="inlineStr"/>
+      <c r="I10" s="30" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>@maworlando</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="24" t="n">
         <v>1049</v>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -7344,53 +8090,53 @@
       <c r="E11" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>martialartsworldorlando.com</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr"/>
       <c r="H11" s="22" t="inlineStr"/>
-      <c r="I11" s="24" t="inlineStr"/>
+      <c r="I11" s="25" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>@alamofencesa</t>
         </is>
       </c>
-      <c r="B12" s="27" t="n">
+      <c r="B12" s="29" t="n">
         <v>88</v>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>fencing</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>alamofencesa.com</t>
         </is>
       </c>
-      <c r="G12" s="26" t="inlineStr"/>
-      <c r="H12" s="26" t="inlineStr"/>
-      <c r="I12" s="28" t="inlineStr"/>
+      <c r="G12" s="27" t="inlineStr"/>
+      <c r="H12" s="27" t="inlineStr"/>
+      <c r="I12" s="30" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>@powerwashproplus</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n">
+      <c r="B13" s="24" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -7406,53 +8152,53 @@
       <c r="E13" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>powerwashproplus.com</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr"/>
       <c r="H13" s="22" t="inlineStr"/>
-      <c r="I13" s="24" t="inlineStr"/>
+      <c r="I13" s="25" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>@bubbledowncarwash</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="29" t="n">
         <v>3598</v>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>car wash</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Tampa, FL</t>
         </is>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="E14" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>bubbledown.com</t>
         </is>
       </c>
-      <c r="G14" s="26" t="inlineStr"/>
-      <c r="H14" s="26" t="inlineStr"/>
-      <c r="I14" s="28" t="inlineStr"/>
+      <c r="G14" s="27" t="inlineStr"/>
+      <c r="H14" s="27" t="inlineStr"/>
+      <c r="I14" s="30" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>@buck_and_sons</t>
         </is>
       </c>
-      <c r="B15" s="23" t="n">
+      <c r="B15" s="24" t="n">
         <v>827</v>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -7468,53 +8214,53 @@
       <c r="E15" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>buckandsons.com</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr"/>
       <c r="H15" s="22" t="inlineStr"/>
-      <c r="I15" s="24" t="inlineStr"/>
+      <c r="I15" s="25" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>@jet_exterior</t>
         </is>
       </c>
-      <c r="B16" s="27" t="n">
+      <c r="B16" s="29" t="n">
         <v>651</v>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>pressure washing</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Jacksonville, FL</t>
         </is>
       </c>
-      <c r="E16" s="25" t="n">
+      <c r="E16" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="F16" s="26" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>jetexterior.com</t>
         </is>
       </c>
-      <c r="G16" s="26" t="inlineStr"/>
-      <c r="H16" s="26" t="inlineStr"/>
-      <c r="I16" s="28" t="inlineStr"/>
+      <c r="G16" s="27" t="inlineStr"/>
+      <c r="H16" s="27" t="inlineStr"/>
+      <c r="I16" s="30" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>@serenitynashville</t>
         </is>
       </c>
-      <c r="B17" s="23" t="n">
+      <c r="B17" s="24" t="n">
         <v>346</v>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -7530,53 +8276,53 @@
       <c r="E17" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>serenitynashville.com</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr"/>
       <c r="H17" s="22" t="inlineStr"/>
-      <c r="I17" s="24" t="inlineStr"/>
+      <c r="I17" s="25" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>@propaintingcharlotte</t>
         </is>
       </c>
-      <c r="B18" s="27" t="n">
+      <c r="B18" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>painting</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>Charlotte, NC</t>
         </is>
       </c>
-      <c r="E18" s="25" t="n">
+      <c r="E18" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>paintingcharlotte.com</t>
         </is>
       </c>
-      <c r="G18" s="26" t="inlineStr"/>
-      <c r="H18" s="26" t="inlineStr"/>
-      <c r="I18" s="28" t="inlineStr"/>
+      <c r="G18" s="27" t="inlineStr"/>
+      <c r="H18" s="27" t="inlineStr"/>
+      <c r="I18" s="30" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>@mclainsmarketkc</t>
         </is>
       </c>
-      <c r="B19" s="23" t="n">
+      <c r="B19" s="24" t="n">
         <v>27000</v>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -7592,53 +8338,53 @@
       <c r="E19" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>mclainskc.com</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr"/>
       <c r="H19" s="22" t="inlineStr"/>
-      <c r="I19" s="24" t="inlineStr"/>
+      <c r="I19" s="25" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>@functional.idaho</t>
         </is>
       </c>
-      <c r="B20" s="27" t="n">
+      <c r="B20" s="29" t="n">
         <v>15000</v>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>gym</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>Boise, ID</t>
         </is>
       </c>
-      <c r="E20" s="25" t="n">
+      <c r="E20" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="F20" s="26" t="inlineStr">
+      <c r="F20" s="28" t="inlineStr">
         <is>
           <t>functionalidaho.com</t>
         </is>
       </c>
-      <c r="G20" s="26" t="inlineStr"/>
-      <c r="H20" s="26" t="inlineStr"/>
-      <c r="I20" s="28" t="inlineStr"/>
+      <c r="G20" s="27" t="inlineStr"/>
+      <c r="H20" s="27" t="inlineStr"/>
+      <c r="I20" s="30" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>@squeekyscarwash</t>
         </is>
       </c>
-      <c r="B21" s="23" t="n">
+      <c r="B21" s="24" t="n">
         <v>927</v>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -7654,53 +8400,53 @@
       <c r="E21" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>squeekyscarwash.com</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr"/>
       <c r="H21" s="22" t="inlineStr"/>
-      <c r="I21" s="24" t="inlineStr"/>
+      <c r="I21" s="25" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>@comalfencesa</t>
         </is>
       </c>
-      <c r="B22" s="27" t="n">
+      <c r="B22" s="29" t="n">
         <v>303</v>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
         <is>
           <t>fencing</t>
         </is>
       </c>
-      <c r="D22" s="26" t="inlineStr">
+      <c r="D22" s="27" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
       </c>
-      <c r="E22" s="25" t="n">
+      <c r="E22" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="F22" s="26" t="inlineStr">
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>comalfence.com</t>
         </is>
       </c>
-      <c r="G22" s="26" t="inlineStr"/>
-      <c r="H22" s="26" t="inlineStr"/>
-      <c r="I22" s="28" t="inlineStr"/>
+      <c r="G22" s="27" t="inlineStr"/>
+      <c r="H22" s="27" t="inlineStr"/>
+      <c r="I22" s="30" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>@mcdaniels_landscaping</t>
         </is>
       </c>
-      <c r="B23" s="23" t="n">
+      <c r="B23" s="24" t="n">
         <v>186</v>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -7716,51 +8462,51 @@
       <c r="E23" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>mcdanielslawncare.com</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr"/>
       <c r="H23" s="22" t="inlineStr"/>
-      <c r="I23" s="24" t="inlineStr"/>
+      <c r="I23" s="25" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>@boldwashjacksonville</t>
         </is>
       </c>
-      <c r="B24" s="27" t="inlineStr"/>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr"/>
+      <c r="C24" s="27" t="inlineStr">
         <is>
           <t>pressure washing</t>
         </is>
       </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="D24" s="27" t="inlineStr">
         <is>
           <t>Jacksonville, FL</t>
         </is>
       </c>
-      <c r="E24" s="25" t="n">
+      <c r="E24" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="F24" s="26" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>pressurewashjacksonvillefl.com</t>
         </is>
       </c>
-      <c r="G24" s="26" t="inlineStr"/>
-      <c r="H24" s="26" t="inlineStr"/>
-      <c r="I24" s="28" t="inlineStr"/>
+      <c r="G24" s="27" t="inlineStr"/>
+      <c r="H24" s="27" t="inlineStr"/>
+      <c r="I24" s="30" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>@woodieswashshack</t>
         </is>
       </c>
-      <c r="B25" s="23" t="n">
+      <c r="B25" s="24" t="n">
         <v>10000</v>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -7776,53 +8522,53 @@
       <c r="E25" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>woodieswash.com</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr"/>
       <c r="H25" s="22" t="inlineStr"/>
-      <c r="I25" s="24" t="inlineStr"/>
+      <c r="I25" s="25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>@idahofitnessfactory</t>
         </is>
       </c>
-      <c r="B26" s="27" t="n">
+      <c r="B26" s="29" t="n">
         <v>6724</v>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C26" s="27" t="inlineStr">
         <is>
           <t>gym</t>
         </is>
       </c>
-      <c r="D26" s="26" t="inlineStr">
+      <c r="D26" s="27" t="inlineStr">
         <is>
           <t>Boise, ID</t>
         </is>
       </c>
-      <c r="E26" s="25" t="n">
+      <c r="E26" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="26" t="inlineStr">
+      <c r="F26" s="28" t="inlineStr">
         <is>
           <t>idahofitnessfactory.com</t>
         </is>
       </c>
-      <c r="G26" s="26" t="inlineStr"/>
-      <c r="H26" s="26" t="inlineStr"/>
-      <c r="I26" s="28" t="inlineStr"/>
+      <c r="G26" s="27" t="inlineStr"/>
+      <c r="H26" s="27" t="inlineStr"/>
+      <c r="I26" s="30" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="inlineStr">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>@bigdanscarwash</t>
         </is>
       </c>
-      <c r="B27" s="23" t="n">
+      <c r="B27" s="24" t="n">
         <v>2433</v>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -7838,53 +8584,53 @@
       <c r="E27" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>bigdanscarwash.com</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr"/>
       <c r="H27" s="22" t="inlineStr"/>
-      <c r="I27" s="24" t="inlineStr"/>
+      <c r="I27" s="25" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t>@aquasoniccarwash</t>
         </is>
       </c>
-      <c r="B28" s="27" t="n">
+      <c r="B28" s="29" t="n">
         <v>1992</v>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C28" s="27" t="inlineStr">
         <is>
           <t>car wash</t>
         </is>
       </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>Tampa, FL</t>
         </is>
       </c>
-      <c r="E28" s="25" t="n">
+      <c r="E28" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="F28" s="26" t="inlineStr">
+      <c r="F28" s="28" t="inlineStr">
         <is>
           <t>aquasoniccarwash.com</t>
         </is>
       </c>
-      <c r="G28" s="26" t="inlineStr"/>
-      <c r="H28" s="26" t="inlineStr"/>
-      <c r="I28" s="28" t="inlineStr"/>
+      <c r="G28" s="27" t="inlineStr"/>
+      <c r="H28" s="27" t="inlineStr"/>
+      <c r="I28" s="30" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>@kcarboristtreecare</t>
         </is>
       </c>
-      <c r="B29" s="23" t="n">
+      <c r="B29" s="24" t="n">
         <v>941</v>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -7900,53 +8646,53 @@
       <c r="E29" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>kcarborist.com</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr"/>
       <c r="H29" s="22" t="inlineStr"/>
-      <c r="I29" s="24" t="inlineStr"/>
+      <c r="I29" s="25" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>@charlottepaintsquad</t>
         </is>
       </c>
-      <c r="B30" s="27" t="n">
+      <c r="B30" s="29" t="n">
         <v>894</v>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C30" s="27" t="inlineStr">
         <is>
           <t>painting</t>
         </is>
       </c>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="D30" s="27" t="inlineStr">
         <is>
           <t>Charlotte, NC</t>
         </is>
       </c>
-      <c r="E30" s="25" t="n">
+      <c r="E30" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="26" t="inlineStr">
+      <c r="F30" s="28" t="inlineStr">
         <is>
           <t>charlottepaintsquad.com</t>
         </is>
       </c>
-      <c r="G30" s="26" t="inlineStr"/>
-      <c r="H30" s="26" t="inlineStr"/>
-      <c r="I30" s="28" t="inlineStr"/>
+      <c r="G30" s="27" t="inlineStr"/>
+      <c r="H30" s="27" t="inlineStr"/>
+      <c r="I30" s="30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>@aquashineexpress</t>
         </is>
       </c>
-      <c r="B31" s="23" t="n">
+      <c r="B31" s="24" t="n">
         <v>438</v>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -7962,53 +8708,53 @@
       <c r="E31" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>aquashineexpress.com</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr"/>
       <c r="H31" s="22" t="inlineStr"/>
-      <c r="I31" s="24" t="inlineStr"/>
+      <c r="I31" s="25" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>@groombarsalon</t>
         </is>
       </c>
-      <c r="B32" s="27" t="n">
+      <c r="B32" s="29" t="n">
         <v>343</v>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C32" s="27" t="inlineStr">
         <is>
           <t>pet grooming</t>
         </is>
       </c>
-      <c r="D32" s="26" t="inlineStr">
+      <c r="D32" s="27" t="inlineStr">
         <is>
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="E32" s="25" t="n">
+      <c r="E32" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="F32" s="26" t="inlineStr">
+      <c r="F32" s="28" t="inlineStr">
         <is>
           <t>groombar.com</t>
         </is>
       </c>
-      <c r="G32" s="26" t="inlineStr"/>
-      <c r="H32" s="26" t="inlineStr"/>
-      <c r="I32" s="28" t="inlineStr"/>
+      <c r="G32" s="27" t="inlineStr"/>
+      <c r="H32" s="27" t="inlineStr"/>
+      <c r="I32" s="30" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="inlineStr">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>@foxheatingandcooling</t>
         </is>
       </c>
-      <c r="B33" s="23" t="n">
+      <c r="B33" s="24" t="n">
         <v>67</v>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -8024,53 +8770,53 @@
       <c r="E33" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>foxhvacpro.com</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr"/>
       <c r="H33" s="22" t="inlineStr"/>
-      <c r="I33" s="24" t="inlineStr"/>
+      <c r="I33" s="25" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>@joescarwashfl</t>
         </is>
       </c>
-      <c r="B34" s="27" t="n">
+      <c r="B34" s="29" t="n">
         <v>57</v>
       </c>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="C34" s="27" t="inlineStr">
         <is>
           <t>car wash</t>
         </is>
       </c>
-      <c r="D34" s="26" t="inlineStr">
+      <c r="D34" s="27" t="inlineStr">
         <is>
           <t>Orlando, FL</t>
         </is>
       </c>
-      <c r="E34" s="25" t="n">
+      <c r="E34" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="F34" s="26" t="inlineStr">
+      <c r="F34" s="28" t="inlineStr">
         <is>
           <t>joescarwashes.com</t>
         </is>
       </c>
-      <c r="G34" s="26" t="inlineStr"/>
-      <c r="H34" s="26" t="inlineStr"/>
-      <c r="I34" s="28" t="inlineStr"/>
+      <c r="G34" s="27" t="inlineStr"/>
+      <c r="H34" s="27" t="inlineStr"/>
+      <c r="I34" s="30" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="A35" s="23" t="inlineStr">
         <is>
           <t>@Johnsonservicescompany</t>
         </is>
       </c>
-      <c r="B35" s="23" t="n">
+      <c r="B35" s="24" t="n">
         <v>26</v>
       </c>
       <c r="C35" s="22" t="inlineStr">
@@ -8086,53 +8832,53 @@
       <c r="E35" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="23" t="inlineStr">
         <is>
           <t>johnsonservicescompany.com</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr"/>
       <c r="H35" s="22" t="inlineStr"/>
-      <c r="I35" s="24" t="inlineStr"/>
+      <c r="I35" s="25" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="26" t="inlineStr">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>@superstarcarwashes</t>
         </is>
       </c>
-      <c r="B36" s="27" t="n">
+      <c r="B36" s="29" t="n">
         <v>17000</v>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C36" s="27" t="inlineStr">
         <is>
           <t>car wash</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="D36" s="27" t="inlineStr">
         <is>
           <t>Phoenix, AZ</t>
         </is>
       </c>
-      <c r="E36" s="25" t="n">
+      <c r="E36" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="F36" s="26" t="inlineStr">
+      <c r="F36" s="28" t="inlineStr">
         <is>
           <t>superstarcarwashaz.com</t>
         </is>
       </c>
-      <c r="G36" s="26" t="inlineStr"/>
-      <c r="H36" s="26" t="inlineStr"/>
-      <c r="I36" s="28" t="inlineStr"/>
+      <c r="G36" s="27" t="inlineStr"/>
+      <c r="H36" s="27" t="inlineStr"/>
+      <c r="I36" s="30" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="inlineStr">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>@poppyandmonroe</t>
         </is>
       </c>
-      <c r="B37" s="23" t="n">
+      <c r="B37" s="24" t="n">
         <v>17000</v>
       </c>
       <c r="C37" s="22" t="inlineStr">
@@ -8148,53 +8894,53 @@
       <c r="E37" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="23" t="inlineStr">
         <is>
           <t>poppyandmonroe.com</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr"/>
       <c r="H37" s="22" t="inlineStr"/>
-      <c r="I37" s="24" t="inlineStr"/>
+      <c r="I37" s="25" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="26" t="inlineStr">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>@ultrashadetattoos</t>
         </is>
       </c>
-      <c r="B38" s="27" t="n">
+      <c r="B38" s="29" t="n">
         <v>6756</v>
       </c>
-      <c r="C38" s="26" t="inlineStr">
+      <c r="C38" s="27" t="inlineStr">
         <is>
           <t>tattoo</t>
         </is>
       </c>
-      <c r="D38" s="26" t="inlineStr">
+      <c r="D38" s="27" t="inlineStr">
         <is>
           <t>Columbus, OH</t>
         </is>
       </c>
-      <c r="E38" s="25" t="n">
+      <c r="E38" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="26" t="inlineStr">
+      <c r="F38" s="28" t="inlineStr">
         <is>
           <t>ultrashadetattoos.com</t>
         </is>
       </c>
-      <c r="G38" s="26" t="inlineStr"/>
-      <c r="H38" s="26" t="inlineStr"/>
-      <c r="I38" s="28" t="inlineStr"/>
+      <c r="G38" s="27" t="inlineStr"/>
+      <c r="H38" s="27" t="inlineStr"/>
+      <c r="I38" s="30" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="inlineStr">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>@fairwaylawns</t>
         </is>
       </c>
-      <c r="B39" s="23" t="n">
+      <c r="B39" s="24" t="n">
         <v>1642</v>
       </c>
       <c r="C39" s="22" t="inlineStr">
@@ -8210,53 +8956,53 @@
       <c r="E39" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="F39" s="22" t="inlineStr">
+      <c r="F39" s="23" t="inlineStr">
         <is>
           <t>fairwaylawns.com</t>
         </is>
       </c>
       <c r="G39" s="22" t="inlineStr"/>
       <c r="H39" s="22" t="inlineStr"/>
-      <c r="I39" s="24" t="inlineStr"/>
+      <c r="I39" s="25" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="26" t="inlineStr">
+      <c r="A40" s="28" t="inlineStr">
         <is>
           <t>@Mobiledetailingexpert</t>
         </is>
       </c>
-      <c r="B40" s="27" t="n">
+      <c r="B40" s="29" t="n">
         <v>765</v>
       </c>
-      <c r="C40" s="26" t="inlineStr">
+      <c r="C40" s="27" t="inlineStr">
         <is>
           <t>detailing</t>
         </is>
       </c>
-      <c r="D40" s="26" t="inlineStr">
+      <c r="D40" s="27" t="inlineStr">
         <is>
           <t>Columbus, OH</t>
         </is>
       </c>
-      <c r="E40" s="25" t="n">
+      <c r="E40" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="26" t="inlineStr">
+      <c r="F40" s="28" t="inlineStr">
         <is>
           <t>mobiledetailingexpert.com</t>
         </is>
       </c>
-      <c r="G40" s="26" t="inlineStr"/>
-      <c r="H40" s="26" t="inlineStr"/>
-      <c r="I40" s="28" t="inlineStr"/>
+      <c r="G40" s="27" t="inlineStr"/>
+      <c r="H40" s="27" t="inlineStr"/>
+      <c r="I40" s="30" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="inlineStr">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>@nashroofingco</t>
         </is>
       </c>
-      <c r="B41" s="23" t="n">
+      <c r="B41" s="24" t="n">
         <v>694</v>
       </c>
       <c r="C41" s="22" t="inlineStr">
@@ -8272,53 +9018,53 @@
       <c r="E41" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="F41" s="22" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
         <is>
           <t>nashvilleroofingco.com</t>
         </is>
       </c>
       <c r="G41" s="22" t="inlineStr"/>
       <c r="H41" s="22" t="inlineStr"/>
-      <c r="I41" s="24" t="inlineStr"/>
+      <c r="I41" s="25" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="26" t="inlineStr">
+      <c r="A42" s="28" t="inlineStr">
         <is>
           <t>@billraganroofing</t>
         </is>
       </c>
-      <c r="B42" s="27" t="n">
+      <c r="B42" s="29" t="n">
         <v>482</v>
       </c>
-      <c r="C42" s="26" t="inlineStr">
+      <c r="C42" s="27" t="inlineStr">
         <is>
           <t>roofing</t>
         </is>
       </c>
-      <c r="D42" s="26" t="inlineStr">
+      <c r="D42" s="27" t="inlineStr">
         <is>
           <t>Nashville, TN</t>
         </is>
       </c>
-      <c r="E42" s="25" t="n">
+      <c r="E42" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="F42" s="26" t="inlineStr">
+      <c r="F42" s="28" t="inlineStr">
         <is>
           <t>billraganroofing.com</t>
         </is>
       </c>
-      <c r="G42" s="26" t="inlineStr"/>
-      <c r="H42" s="26" t="inlineStr"/>
-      <c r="I42" s="28" t="inlineStr"/>
+      <c r="G42" s="27" t="inlineStr"/>
+      <c r="H42" s="27" t="inlineStr"/>
+      <c r="I42" s="30" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="22" t="inlineStr">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t>@peppyheatingcooling</t>
         </is>
       </c>
-      <c r="B43" s="23" t="inlineStr"/>
+      <c r="B43" s="24" t="inlineStr"/>
       <c r="C43" s="22" t="inlineStr">
         <is>
           <t>hvac</t>
@@ -8332,53 +9078,53 @@
       <c r="E43" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="F43" s="22" t="inlineStr">
+      <c r="F43" s="23" t="inlineStr">
         <is>
           <t>callpeppy.com</t>
         </is>
       </c>
       <c r="G43" s="22" t="inlineStr"/>
       <c r="H43" s="22" t="inlineStr"/>
-      <c r="I43" s="24" t="inlineStr"/>
+      <c r="I43" s="25" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="26" t="inlineStr">
+      <c r="A44" s="28" t="inlineStr">
         <is>
           <t>@AutoBellCarWash</t>
         </is>
       </c>
-      <c r="B44" s="27" t="n">
+      <c r="B44" s="29" t="n">
         <v>6132</v>
       </c>
-      <c r="C44" s="26" t="inlineStr">
+      <c r="C44" s="27" t="inlineStr">
         <is>
           <t>car wash</t>
         </is>
       </c>
-      <c r="D44" s="26" t="inlineStr">
+      <c r="D44" s="27" t="inlineStr">
         <is>
           <t>Charlotte, NC</t>
         </is>
       </c>
-      <c r="E44" s="25" t="n">
+      <c r="E44" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="26" t="inlineStr">
+      <c r="F44" s="28" t="inlineStr">
         <is>
           <t>autobell.com</t>
         </is>
       </c>
-      <c r="G44" s="26" t="inlineStr"/>
-      <c r="H44" s="26" t="inlineStr"/>
-      <c r="I44" s="28" t="inlineStr"/>
+      <c r="G44" s="27" t="inlineStr"/>
+      <c r="H44" s="27" t="inlineStr"/>
+      <c r="I44" s="30" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="22" t="inlineStr">
+      <c r="A45" s="23" t="inlineStr">
         <is>
           <t>@tidalwaveautospa</t>
         </is>
       </c>
-      <c r="B45" s="23" t="n">
+      <c r="B45" s="24" t="n">
         <v>4431</v>
       </c>
       <c r="C45" s="22" t="inlineStr">
@@ -8394,14 +9140,14 @@
       <c r="E45" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="F45" s="22" t="inlineStr">
+      <c r="F45" s="23" t="inlineStr">
         <is>
           <t>tidalwaveautospa.com</t>
         </is>
       </c>
       <c r="G45" s="22" t="inlineStr"/>
       <c r="H45" s="22" t="inlineStr"/>
-      <c r="I45" s="24" t="inlineStr"/>
+      <c r="I45" s="25" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:I45"/>
@@ -8424,6 +9170,90 @@
       <formula1>"sim,não"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId82"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8457,24 +9287,24 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>Negócio</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>Site</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t>O que verificar</t>
         </is>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Championship Martial Arts</t>
         </is>
@@ -8484,31 +9314,31 @@
           <t>championshipmartialarts.com</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Os e-mails capturados são de OUTRAS franquias (d-a-m.ca, pakskarate.com, randori-pro.com). Achar o contato da unidade de Orlando antes de abordar.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Kansas City Tree Services</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>kansascitytreeservices.net</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>Telefone aparente 816-555-7890, padrão clássico de placeholder. Pode ser site de lead-broker e não negócio real. Confirmar no Google Maps antes.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Purrfect Grooming</t>
         </is>
@@ -8518,31 +9348,31 @@
           <t>purrfectgrooming.pet</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>A sede parece ser Doral/Miami, não Orlando. O site é ótimo alvo, só ajuste a cidade na conversa.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>Redes grandes (nota 1-3)</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>autobell.com, tidalwaveautospa.com, superstarcarwashes...</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>Site bom e agência contratada: não são venda. Servem para seguir e comentar, porque colocam você no grafo social do nicho.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>E-mails genéricos</t>
         </is>
@@ -8552,7 +9382,7 @@
           <t>info@, contact@, support@</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Chegam na caixa geral e costumam morrer lá. O Instagram continua sendo o canal principal: e-mail é reforço, não substituto.</t>
         </is>

--- a/prospeccao/prospeccao-rvland.xlsx
+++ b/prospeccao/prospeccao-rvland.xlsx
@@ -15,8 +15,8 @@
     <sheet name="Avisos" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leads'!$A$4:$O$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Prioridade'!$A$4:$O$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leads'!$A$4:$P$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Prioridade'!$A$4:$P$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Instagram'!$A$4:$I$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -155,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -227,8 +227,14 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -1750,7 +1756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:P70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1767,7 +1773,8 @@
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="62" customWidth="1" min="15" max="15"/>
+    <col width="58" customWidth="1" min="15" max="15"/>
+    <col width="72" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1780,7 +1787,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ordenado por potencial. Site, print, Instagram e e-mail são clicáveis: confira cada avaliação você mesmo.</t>
+          <t>Site, print, Instagram e e-mail são clicáveis. As duas últimas colunas são coisas diferentes: o diagnóstico é o que EU vi no site hoje; 'Como abordar' é o que VOCÊ faz.</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1864,12 @@
       </c>
       <c r="O4" s="10" t="inlineStr">
         <is>
-          <t>Ângulo de abordagem</t>
+          <t>O que vi no site (diagnóstico)</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="inlineStr">
+        <is>
+          <t>Como abordar (o que fazer)</t>
         </is>
       </c>
     </row>
@@ -1919,6 +1931,11 @@
       <c r="O5" s="25" t="inlineStr">
         <is>
           <t>Site de 2013 com botoes bisotados; detailing premium (pacotes de USD 350) = tem caixa; redesign completo + booking</t>
+        </is>
+      </c>
+      <c r="P5" s="25" t="inlineStr">
+        <is>
+          <t>SEM IG e SEM e-mail no site. Ache 'Macron Mobile Detailing Columbus' no Google Maps/Facebook, ou use o formulário do próprio site. Gancho: mande a prévia junto de 'seu trabalho é premium, o site está em 2013'. Alvo nº1 da lista.</t>
         </is>
       </c>
     </row>
@@ -1978,6 +1995,11 @@
           <t>Layout anos 2000, logo clipart, fundo de bolhas; 2 unidades familiares; redesign + booking</t>
         </is>
       </c>
+      <c r="P6" s="30" t="inlineStr">
+        <is>
+          <t>SEM canal direto no site. Procure 'Octopus Car Wash' no Maps/Facebook. Gancho: print lado a lado (bolhas e clipart) contra a prévia moderna. 2 unidades familiares = fala com o dono.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="21" t="n">
@@ -2035,6 +2057,11 @@
           <t>Template generico ~2010, 1 unidade + loja de conveniencia; redesign completo</t>
         </is>
       </c>
+      <c r="P7" s="25" t="inlineStr">
+        <is>
+          <t>SEM canal direto no site. Buscar no Maps/Facebook. Gancho: 1 unidade + loja de conveniência; prévia com serviços, preços e horário bem visíveis.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="n">
@@ -2106,6 +2133,11 @@
           <t>No ar desde 2001, layout 2012, embed YouTube antigo; historia forte pra contar num site novo</t>
         </is>
       </c>
+      <c r="P8" s="30" t="inlineStr">
+        <is>
+          <t>DM no @curbsidemobiledetailing (1.583) ou e-mail info@. Gancho: no ar desde 2001 é história forte que o site atual esconde; prévia destacando os 20+ anos.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="21" t="n">
@@ -2171,6 +2203,11 @@
           <t>Hero quebrado (secao em branco, form solto); multi-unidades em Orlando; consertar = venda facil de mostrar</t>
         </is>
       </c>
+      <c r="P9" s="25" t="inlineStr">
+        <is>
+          <t>CUIDADO: os e-mails são de outras franquias. Ache a unidade de Orlando no Maps. Gancho: o hero da home está QUEBRADO (seção em branco com formulário solto); o print é o argumento mais fácil da lista inteira.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="26" t="n">
@@ -2240,6 +2277,11 @@
       <c r="O10" s="30" t="inlineStr">
         <is>
           <t>Hero quebrado com sobreposicao de logo; frota adesivada (investe em marca); ATENCAO: sede em Doral/Miami</t>
+        </is>
+      </c>
+      <c r="P10" s="30" t="inlineStr">
+        <is>
+          <t>DM no @purrfectgrooming.pet (4.980) ou e-mail contactus@. Gancho: hero quebrado com logo sobreposto; frota adesivada mostra que investem em marca, mas o site não acompanha. Confirme a cidade antes (parece Doral, não Orlando).</t>
         </is>
       </c>
     </row>
@@ -2303,6 +2345,11 @@
           <t>Copyright 2011, template bootstrap velho, form denso; negocio real com 2 telefones</t>
         </is>
       </c>
+      <c r="P11" s="25" t="inlineStr">
+        <is>
+          <t>SEM canal direto. Maps/Facebook. Gancho: copyright 2011 e formulário denso; prévia com pedido de orçamento em 3 campos.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="26" t="n">
@@ -2366,6 +2413,11 @@
       <c r="O12" s="30" t="inlineStr">
         <is>
           <t>Divi roxo datado ~2015; oficina familiar desde 1979; email do dono (mickey@) exposto no site</t>
+        </is>
+      </c>
+      <c r="P12" s="30" t="inlineStr">
+        <is>
+          <t>E-mail DIRETO DO DONO: mickey@phoenixautoshop.com. Gancho: oficina de família desde 1979 com site Divi roxo de 2015; prévia que respeite a história e mostre agendamento.</t>
         </is>
       </c>
     </row>
@@ -2427,6 +2479,11 @@
       <c r="O13" s="25" t="inlineStr">
         <is>
           <t>Visual datado, video com texto arial; rede local pequena de Phoenix</t>
+        </is>
+      </c>
+      <c r="P13" s="25" t="inlineStr">
+        <is>
+          <t>SEM canal direto. Maps. Gancho: visual datado com texto em Arial sobre vídeo; rede local pequena de Phoenix.</t>
         </is>
       </c>
     </row>
@@ -2486,6 +2543,11 @@
           <t>Weebly DIY, tipografia generica, fotos reais; dono fez sozinho</t>
         </is>
       </c>
+      <c r="P14" s="30" t="inlineStr">
+        <is>
+          <t>SEM canal direto. Maps/Facebook. Gancho: Weebly feito pelo próprio dono, ele já sabe que o site é fraco; prévia com galeria das cercas reais.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="21" t="n">
@@ -2555,6 +2617,11 @@
       <c r="O15" s="25" t="inlineStr">
         <is>
           <t>Logo 3D anos 2000, botoes de ticket; desde 1967, Carrier dealer = caixa; decisao pode ser lenta</t>
+        </is>
+      </c>
+      <c r="P15" s="25" t="inlineStr">
+        <is>
+          <t>E-mail tom@ ou max@ (parecem os sócios) ou DM @westernhvac (2.281). Gancho: desde 1967 e Carrier dealer, mas logo 3D dos anos 2000. Empresa grande: espere decisão mais lenta.</t>
         </is>
       </c>
     </row>
@@ -2618,6 +2685,11 @@
           <t>Template 2012 com foto de banco de imagem; info@ visivel no header</t>
         </is>
       </c>
+      <c r="P16" s="30" t="inlineStr">
+        <is>
+          <t>E-mail info@sciotolandscaping.com. Gancho: template de 2012 usando FOTO DE BANCO DE IMAGEM; prévia com os jardins reais que eles fizeram.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="21" t="n">
@@ -2683,6 +2755,11 @@
           <t>Logo clipart, WP basico; 49 reviews 4.8 = negocio bom com site fraco</t>
         </is>
       </c>
+      <c r="P17" s="25" t="inlineStr">
+        <is>
+          <t>E-mail straightedgepp@gmail.com (Gmail = negócio pequeno, o dono lê). Gancho: 49 avaliações 4.8 estrelas e o site não mostra isso em lugar nenhum.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="26" t="n">
@@ -2754,6 +2831,11 @@
           <t>Wix DIY com logo duplicado gigante e layout desalinhado; tem booking</t>
         </is>
       </c>
+      <c r="P18" s="30" t="inlineStr">
+        <is>
+          <t>DM no @allcreaturespetgrooming (3.277) ou e-mail info@. Gancho: Wix com logo duplicado gigante e layout desalinhado; print lado a lado resolve a conversa.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="21" t="n">
@@ -2821,6 +2903,11 @@
           <t>Layout ~2015 (Duda), logo simples; padaria artesanal com IG</t>
         </is>
       </c>
+      <c r="P19" s="25" t="inlineStr">
+        <is>
+          <t>DM no @bloombakingco (4.204). SEM e-mail no site. Gancho: padaria artesanal bonita com site sem graça; prévia com as fotos dos produtos que já postam no IG.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="26" t="n">
@@ -2886,6 +2973,11 @@
           <t>GoDaddy DIY, 1 unidade; template razoavel mas generico</t>
         </is>
       </c>
+      <c r="P20" s="30" t="inlineStr">
+        <is>
+          <t>E-mail bluswancarwash@gmail.com. Gancho: GoDaddy DIY genérico; prévia com planos e preços claros.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="21" t="n">
@@ -2951,6 +3043,11 @@
       <c r="O21" s="25" t="inlineStr">
         <is>
           <t>Layout centrado antigo; customerservice@ exposto; negocio estabelecido</t>
+        </is>
+      </c>
+      <c r="P21" s="25" t="inlineStr">
+        <is>
+          <t>E-mail customerservice@alamofencesa.com. Gancho: layout centrado antigo. Extra: o IG tem só 88 seguidores, dá pra oferecer site + presença social.</t>
         </is>
       </c>
     </row>
@@ -3014,6 +3111,11 @@
           <t>WP generico, hero cru; empresa 25+ anos</t>
         </is>
       </c>
+      <c r="P22" s="30" t="inlineStr">
+        <is>
+          <t>E-mail service@ims365hvac.com. Gancho: 25+ anos de experiência num WordPress genérico com hero cru.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="21" t="n">
@@ -3081,6 +3183,11 @@
           <t>Logo anos 90, layout mediano; academia local com programas</t>
         </is>
       </c>
+      <c r="P23" s="25" t="inlineStr">
+        <is>
+          <t>DM no @maworlando (1.049) ou e-mail orlandoadmin@. Gancho: logo dos anos 90; prévia com formulário de aula experimental, que é como academia capta.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="26" t="n">
@@ -3148,6 +3255,11 @@
           <t>Squarespace generico, logo clipart, hero fraco; facil mostrar upgrade</t>
         </is>
       </c>
+      <c r="P24" s="30" t="inlineStr">
+        <is>
+          <t>E-mail powerwashproplus@gmail.com. Gancho: Squarespace genérico com logo clipart. O IG tem 7 seguidores: está começando do zero, bom candidato a site + social.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="21" t="n">
@@ -3219,6 +3331,11 @@
           <t>Artista solo desde 1997; site simples escuro; decisao rapida, IG e a vida do tatuador</t>
         </is>
       </c>
+      <c r="P25" s="25" t="inlineStr">
+        <is>
+          <t>DM no @wes_tattoos_columbus (11K seguidores!). Gancho: artista solo desde 1997, decisão rápida e sem comitê; IG forte mas site simples, prévia com galeria destacada.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="26" t="n">
@@ -3290,6 +3407,11 @@
           <t>Site ok porem copyright 2016; IG ativo 3.5k; abordagem por relacionamento</t>
         </is>
       </c>
+      <c r="P26" s="30" t="inlineStr">
+        <is>
+          <t>Morno: so vale se sobrar tempo depois dos quentes. Canal: DM em @bubbledowncarwash.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="21" t="n">
@@ -3355,6 +3477,11 @@
           <t>Site decente mas email no Gmail (DIY vibe); familia</t>
         </is>
       </c>
+      <c r="P27" s="25" t="inlineStr">
+        <is>
+          <t>Morno: so vale se sobrar tempo depois dos quentes. Canal: e-mail do site.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="26" t="n">
@@ -3422,6 +3549,11 @@
           <t>Desde 1971, site funcional porem datado; empresa grande familiar</t>
         </is>
       </c>
+      <c r="P28" s="30" t="inlineStr">
+        <is>
+          <t>Morno: so vale se sobrar tempo depois dos quentes. Canal: DM em @buck_and_sons.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="21" t="n">
@@ -3493,6 +3625,11 @@
           <t>Site limpo mas datado (2022); nail bar bonito</t>
         </is>
       </c>
+      <c r="P29" s="25" t="inlineStr">
+        <is>
+          <t>Morno: so vale se sobrar tempo depois dos quentes. Canal: DM em @serenitynashville.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="26" t="n">
@@ -3560,6 +3697,11 @@
           <t>Logo anos 2000, layout denso; info@ visivel</t>
         </is>
       </c>
+      <c r="P30" s="30" t="inlineStr">
+        <is>
+          <t>Morno: so vale se sobrar tempo depois dos quentes. Canal: DM em @propaintingcharlotte.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="21" t="n">
@@ -3631,6 +3773,11 @@
           <t>Wix razoavel, logo fraco; IG 651</t>
         </is>
       </c>
+      <c r="P31" s="25" t="inlineStr">
+        <is>
+          <t>Morno: so vale se sobrar tempo depois dos quentes. Canal: DM em @jet_exterior.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="26" t="n">
@@ -3696,6 +3843,11 @@
           <t>Desde 1957; template funcional datado-ish</t>
         </is>
       </c>
+      <c r="P32" s="30" t="inlineStr">
+        <is>
+          <t>Morno: so vale se sobrar tempo depois dos quentes. Canal: e-mail do site.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="21" t="n">
@@ -3759,6 +3911,11 @@
           <t>Squarespace ok, hero com contraste ruim; desde 1945</t>
         </is>
       </c>
+      <c r="P33" s="25" t="inlineStr">
+        <is>
+          <t>Morno: so vale se sobrar tempo depois dos quentes. Canal: DM em @mclainsmarketkc.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="26" t="n">
@@ -3830,6 +3987,11 @@
           <t>Template moderno ok; pouca dor aparente</t>
         </is>
       </c>
+      <c r="P34" s="30" t="inlineStr">
+        <is>
+          <t>Morno: so vale se sobrar tempo depois dos quentes. Canal: DM em @squeekyscarwash.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="21" t="n">
@@ -3901,6 +4063,11 @@
           <t>Razoavel e funcional</t>
         </is>
       </c>
+      <c r="P35" s="25" t="inlineStr">
+        <is>
+          <t>Morno: so vale se sobrar tempo depois dos quentes. Canal: DM em @comalfencesa.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="26" t="n">
@@ -3968,6 +4135,11 @@
           <t>Carregado mas funcional; 630 reviews; familia</t>
         </is>
       </c>
+      <c r="P36" s="30" t="inlineStr">
+        <is>
+          <t>Morno: so vale se sobrar tempo depois dos quentes. Canal: DM em @functional.idaho.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="21" t="n">
@@ -4039,6 +4211,11 @@
           <t>Site razoavel com bug visual no hero; mike@ exposto</t>
         </is>
       </c>
+      <c r="P37" s="25" t="inlineStr">
+        <is>
+          <t>Morno: so vale se sobrar tempo depois dos quentes. Canal: DM em @mcdaniels_landscaping.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="26" t="n">
@@ -4108,6 +4285,11 @@
           <t>Site ok generico; IG com 0 seguidores = comecando presenca social</t>
         </is>
       </c>
+      <c r="P38" s="30" t="inlineStr">
+        <is>
+          <t>Morno: so vale se sobrar tempo depois dos quentes. Canal: DM em @boldwashjacksonville.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
@@ -4173,6 +4355,11 @@
           <t>SUSPEITA de lead-broker: telefone placeholder 816-555-7890 na foto; verificar se e negocio real</t>
         </is>
       </c>
+      <c r="P39" s="25" t="inlineStr">
+        <is>
+          <t>Morno: so vale se sobrar tempo depois dos quentes. Canal: e-mail do site.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="26" t="n">
@@ -4236,6 +4423,11 @@
       <c r="O40" s="30" t="inlineStr">
         <is>
           <t>Moderno com social proof; desde 1976</t>
+        </is>
+      </c>
+      <c r="P40" s="30" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
         </is>
       </c>
     </row>
@@ -4295,6 +4487,11 @@
           <t>Moderno com fotos reais da equipe</t>
         </is>
       </c>
+      <c r="P41" s="25" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="26" t="n">
@@ -4362,6 +4559,11 @@
           <t>Site bom; IG com so 57 seguidores (oportunidade social, nao site)</t>
         </is>
       </c>
+      <c r="P42" s="30" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
@@ -4433,6 +4635,11 @@
           <t>Site moderno bom</t>
         </is>
       </c>
+      <c r="P43" s="25" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="26" t="n">
@@ -4504,6 +4711,11 @@
           <t>Marca forte, 18+ unidades, IG 10K; provavelmente tem agencia</t>
         </is>
       </c>
+      <c r="P44" s="30" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
@@ -4571,6 +4783,11 @@
           <t>Site moderno; rede regional</t>
         </is>
       </c>
+      <c r="P45" s="25" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="26" t="n">
@@ -4642,6 +4859,11 @@
           <t>Site moderno</t>
         </is>
       </c>
+      <c r="P46" s="30" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="21" t="n">
@@ -4709,6 +4931,11 @@
           <t>Grande (4 cidades TX), video no hero</t>
         </is>
       </c>
+      <c r="P47" s="25" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="26" t="n">
@@ -4776,6 +5003,11 @@
           <t>Moderno; 10+ unidades</t>
         </is>
       </c>
+      <c r="P48" s="30" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="21" t="n">
@@ -4847,6 +5079,11 @@
           <t>Moderno, badges 2026</t>
         </is>
       </c>
+      <c r="P49" s="25" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="26" t="n">
@@ -4918,6 +5155,11 @@
           <t>Lead-gen moderno</t>
         </is>
       </c>
+      <c r="P50" s="30" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="21" t="n">
@@ -4989,6 +5231,11 @@
           <t>Moderno; franchising no menu</t>
         </is>
       </c>
+      <c r="P51" s="25" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="26" t="n">
@@ -5054,6 +5301,11 @@
           <t>Site bom com precos claros</t>
         </is>
       </c>
+      <c r="P52" s="30" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="21" t="n">
@@ -5119,6 +5371,11 @@
           <t>Moderno decente</t>
         </is>
       </c>
+      <c r="P53" s="25" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="26" t="n">
@@ -5184,6 +5441,11 @@
           <t>Site moderno bonito; hello@ exposto</t>
         </is>
       </c>
+      <c r="P54" s="30" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="21" t="n">
@@ -5249,6 +5511,11 @@
       <c r="O55" s="25" t="inlineStr">
         <is>
           <t>Site ok com badges de rating</t>
+        </is>
+      </c>
+      <c r="P55" s="25" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
         </is>
       </c>
     </row>
@@ -5312,6 +5579,11 @@
           <t>Lead-gen competente</t>
         </is>
       </c>
+      <c r="P56" s="30" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="21" t="n">
@@ -5377,6 +5649,11 @@
           <t>Site excelente</t>
         </is>
       </c>
+      <c r="P57" s="25" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="26" t="n">
@@ -5444,6 +5721,11 @@
           <t>Rede grande AZ, IG 17K</t>
         </is>
       </c>
+      <c r="P58" s="30" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="21" t="n">
@@ -5509,6 +5791,11 @@
           <t>Moderno com booking 60s</t>
         </is>
       </c>
+      <c r="P59" s="25" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="26" t="n">
@@ -5580,6 +5867,11 @@
           <t>Plataforma 80+ cidades, nao local</t>
         </is>
       </c>
+      <c r="P60" s="30" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="21" t="n">
@@ -5645,6 +5937,11 @@
           <t>Moderno bonito</t>
         </is>
       </c>
+      <c r="P61" s="25" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="26" t="n">
@@ -5706,6 +6003,11 @@
           <t>Branding forte com mascote</t>
         </is>
       </c>
+      <c r="P62" s="30" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="21" t="n">
@@ -5773,6 +6075,11 @@
           <t>Rede multi-estado, 78k reviews</t>
         </is>
       </c>
+      <c r="P63" s="25" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="26" t="n">
@@ -5838,6 +6145,11 @@
       <c r="O64" s="30" t="inlineStr">
         <is>
           <t>Squarespace minimal chique</t>
+        </is>
+      </c>
+      <c r="P64" s="30" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
         </is>
       </c>
     </row>
@@ -5897,6 +6209,11 @@
           <t>Moderno; escala nacional</t>
         </is>
       </c>
+      <c r="P65" s="25" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="26" t="n">
@@ -5964,6 +6281,11 @@
           <t>Site forte estilo HubSpot com calculadora</t>
         </is>
       </c>
+      <c r="P66" s="30" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="21" t="n">
@@ -6035,6 +6357,11 @@
           <t>Moderno forte</t>
         </is>
       </c>
+      <c r="P67" s="25" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="26" t="n">
@@ -6102,6 +6429,11 @@
           <t>Site premium chique</t>
         </is>
       </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="21" t="n">
@@ -6169,6 +6501,11 @@
           <t>Corporacao 200+ unidades</t>
         </is>
       </c>
+      <c r="P69" s="25" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="26" t="n">
@@ -6232,9 +6569,14 @@
           <t>Corporacao 75+ unidades</t>
         </is>
       </c>
+      <c r="P70" s="30" t="inlineStr">
+        <is>
+          <t>NAO abordar para venda: o site ja e bom (ou e rede grande com agencia). Use so para seguir e comentar, para entrar no grafo do nicho.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O70"/>
+  <autoFilter ref="A4:P70"/>
   <conditionalFormatting sqref="A5:A70">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>8</formula>
@@ -6495,7 +6837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6507,12 +6849,13 @@
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="58" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="74" customWidth="1" min="10" max="10"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -6525,7 +6868,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Potencial 6+. Fluxo: seguir → comentar 2 ou 3 dias → mandar a DM com a prévia pronta.</t>
+          <t>Potencial 6+. Leia a coluna COMO ABORDAR: ela diz o canal e o gancho de cada um. Fluxo: seguir → comentar 2 ou 3 dias → mandar a DM com a prévia pronta.</t>
         </is>
       </c>
     </row>
@@ -6577,30 +6920,35 @@
       </c>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>Ângulo de abordagem</t>
+          <t>COMO ABORDAR (faça isto)</t>
         </is>
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
+          <t>O que vi no site (diagnóstico)</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L4" s="10" t="inlineStr">
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>Seguiu em</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>Comentou em</t>
         </is>
       </c>
-      <c r="N4" s="10" t="inlineStr">
+      <c r="O4" s="10" t="inlineStr">
         <is>
           <t>DM enviada em</t>
         </is>
       </c>
-      <c r="O4" s="10" t="inlineStr">
+      <c r="P4" s="10" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -6638,20 +6986,25 @@
       <c r="G5" s="22" t="inlineStr"/>
       <c r="H5" s="24" t="inlineStr"/>
       <c r="I5" s="22" t="inlineStr"/>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="J5" s="31" t="inlineStr">
+        <is>
+          <t>SEM IG e SEM e-mail no site. Ache 'Macron Mobile Detailing Columbus' no Google Maps/Facebook, ou use o formulário do próprio site. Gancho: mande a prévia junto de 'seu trabalho é premium, o site está em 2013'. Alvo nº1 da lista.</t>
+        </is>
+      </c>
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t>Site de 2013 com botoes bisotados; detailing premium (pacotes de USD 350) = tem caixa; redesign completo + booking</t>
         </is>
       </c>
-      <c r="K5" s="22" t="inlineStr">
+      <c r="L5" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L5" s="31" t="inlineStr"/>
-      <c r="M5" s="31" t="inlineStr"/>
-      <c r="N5" s="31" t="inlineStr"/>
-      <c r="O5" s="25" t="inlineStr"/>
+      <c r="M5" s="32" t="inlineStr"/>
+      <c r="N5" s="32" t="inlineStr"/>
+      <c r="O5" s="32" t="inlineStr"/>
+      <c r="P5" s="22" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="26" t="n">
@@ -6685,20 +7038,25 @@
       <c r="G6" s="27" t="inlineStr"/>
       <c r="H6" s="29" t="inlineStr"/>
       <c r="I6" s="27" t="inlineStr"/>
-      <c r="J6" s="27" t="inlineStr">
+      <c r="J6" s="33" t="inlineStr">
+        <is>
+          <t>SEM canal direto no site. Procure 'Octopus Car Wash' no Maps/Facebook. Gancho: print lado a lado (bolhas e clipart) contra a prévia moderna. 2 unidades familiares = fala com o dono.</t>
+        </is>
+      </c>
+      <c r="K6" s="30" t="inlineStr">
         <is>
           <t>Layout anos 2000, logo clipart, fundo de bolhas; 2 unidades familiares; redesign + booking</t>
         </is>
       </c>
-      <c r="K6" s="27" t="inlineStr">
+      <c r="L6" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L6" s="32" t="inlineStr"/>
-      <c r="M6" s="32" t="inlineStr"/>
-      <c r="N6" s="32" t="inlineStr"/>
-      <c r="O6" s="30" t="inlineStr"/>
+      <c r="M6" s="34" t="inlineStr"/>
+      <c r="N6" s="34" t="inlineStr"/>
+      <c r="O6" s="34" t="inlineStr"/>
+      <c r="P6" s="27" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="21" t="n">
@@ -6732,20 +7090,25 @@
       <c r="G7" s="22" t="inlineStr"/>
       <c r="H7" s="24" t="inlineStr"/>
       <c r="I7" s="22" t="inlineStr"/>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="J7" s="31" t="inlineStr">
+        <is>
+          <t>SEM canal direto no site. Buscar no Maps/Facebook. Gancho: 1 unidade + loja de conveniência; prévia com serviços, preços e horário bem visíveis.</t>
+        </is>
+      </c>
+      <c r="K7" s="25" t="inlineStr">
         <is>
           <t>Template generico ~2010, 1 unidade + loja de conveniencia; redesign completo</t>
         </is>
       </c>
-      <c r="K7" s="22" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L7" s="31" t="inlineStr"/>
-      <c r="M7" s="31" t="inlineStr"/>
-      <c r="N7" s="31" t="inlineStr"/>
-      <c r="O7" s="25" t="inlineStr"/>
+      <c r="M7" s="32" t="inlineStr"/>
+      <c r="N7" s="32" t="inlineStr"/>
+      <c r="O7" s="32" t="inlineStr"/>
+      <c r="P7" s="22" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="26" t="n">
@@ -6789,20 +7152,25 @@
           <t>info@curbsidemobiledetailing.com</t>
         </is>
       </c>
-      <c r="J8" s="27" t="inlineStr">
+      <c r="J8" s="33" t="inlineStr">
+        <is>
+          <t>DM no @curbsidemobiledetailing (1.583) ou e-mail info@. Gancho: no ar desde 2001 é história forte que o site atual esconde; prévia destacando os 20+ anos.</t>
+        </is>
+      </c>
+      <c r="K8" s="30" t="inlineStr">
         <is>
           <t>No ar desde 2001, layout 2012, embed YouTube antigo; historia forte pra contar num site novo</t>
         </is>
       </c>
-      <c r="K8" s="27" t="inlineStr">
+      <c r="L8" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L8" s="32" t="inlineStr"/>
-      <c r="M8" s="32" t="inlineStr"/>
-      <c r="N8" s="32" t="inlineStr"/>
-      <c r="O8" s="30" t="inlineStr"/>
+      <c r="M8" s="34" t="inlineStr"/>
+      <c r="N8" s="34" t="inlineStr"/>
+      <c r="O8" s="34" t="inlineStr"/>
+      <c r="P8" s="27" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="21" t="n">
@@ -6840,20 +7208,25 @@
           <t>p.paquet@d-a-m.ca / holsej@pakskarate.com / capecoral@randori-pro.com</t>
         </is>
       </c>
-      <c r="J9" s="22" t="inlineStr">
+      <c r="J9" s="31" t="inlineStr">
+        <is>
+          <t>CUIDADO: os e-mails são de outras franquias. Ache a unidade de Orlando no Maps. Gancho: o hero da home está QUEBRADO (seção em branco com formulário solto); o print é o argumento mais fácil da lista inteira.</t>
+        </is>
+      </c>
+      <c r="K9" s="25" t="inlineStr">
         <is>
           <t>Hero quebrado (secao em branco, form solto); multi-unidades em Orlando; consertar = venda facil de mostrar</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="L9" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L9" s="31" t="inlineStr"/>
-      <c r="M9" s="31" t="inlineStr"/>
-      <c r="N9" s="31" t="inlineStr"/>
-      <c r="O9" s="25" t="inlineStr"/>
+      <c r="M9" s="32" t="inlineStr"/>
+      <c r="N9" s="32" t="inlineStr"/>
+      <c r="O9" s="32" t="inlineStr"/>
+      <c r="P9" s="22" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="26" t="n">
@@ -6897,20 +7270,25 @@
           <t>contactus@purrfectgrooming.pet</t>
         </is>
       </c>
-      <c r="J10" s="27" t="inlineStr">
+      <c r="J10" s="33" t="inlineStr">
+        <is>
+          <t>DM no @purrfectgrooming.pet (4.980) ou e-mail contactus@. Gancho: hero quebrado com logo sobreposto; frota adesivada mostra que investem em marca, mas o site não acompanha. Confirme a cidade antes (parece Doral, não Orlando).</t>
+        </is>
+      </c>
+      <c r="K10" s="30" t="inlineStr">
         <is>
           <t>Hero quebrado com sobreposicao de logo; frota adesivada (investe em marca); ATENCAO: sede em Doral/Miami</t>
         </is>
       </c>
-      <c r="K10" s="27" t="inlineStr">
+      <c r="L10" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L10" s="32" t="inlineStr"/>
-      <c r="M10" s="32" t="inlineStr"/>
-      <c r="N10" s="32" t="inlineStr"/>
-      <c r="O10" s="30" t="inlineStr"/>
+      <c r="M10" s="34" t="inlineStr"/>
+      <c r="N10" s="34" t="inlineStr"/>
+      <c r="O10" s="34" t="inlineStr"/>
+      <c r="P10" s="27" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="21" t="n">
@@ -6944,20 +7322,25 @@
       <c r="G11" s="22" t="inlineStr"/>
       <c r="H11" s="24" t="inlineStr"/>
       <c r="I11" s="22" t="inlineStr"/>
-      <c r="J11" s="22" t="inlineStr">
+      <c r="J11" s="31" t="inlineStr">
+        <is>
+          <t>SEM canal direto. Maps/Facebook. Gancho: copyright 2011 e formulário denso; prévia com pedido de orçamento em 3 campos.</t>
+        </is>
+      </c>
+      <c r="K11" s="25" t="inlineStr">
         <is>
           <t>Copyright 2011, template bootstrap velho, form denso; negocio real com 2 telefones</t>
         </is>
       </c>
-      <c r="K11" s="22" t="inlineStr">
+      <c r="L11" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L11" s="31" t="inlineStr"/>
-      <c r="M11" s="31" t="inlineStr"/>
-      <c r="N11" s="31" t="inlineStr"/>
-      <c r="O11" s="25" t="inlineStr"/>
+      <c r="M11" s="32" t="inlineStr"/>
+      <c r="N11" s="32" t="inlineStr"/>
+      <c r="O11" s="32" t="inlineStr"/>
+      <c r="P11" s="22" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="26" t="n">
@@ -6995,20 +7378,25 @@
           <t>mickey@phoenixautoshop.com</t>
         </is>
       </c>
-      <c r="J12" s="27" t="inlineStr">
+      <c r="J12" s="33" t="inlineStr">
+        <is>
+          <t>E-mail DIRETO DO DONO: mickey@phoenixautoshop.com. Gancho: oficina de família desde 1979 com site Divi roxo de 2015; prévia que respeite a história e mostre agendamento.</t>
+        </is>
+      </c>
+      <c r="K12" s="30" t="inlineStr">
         <is>
           <t>Divi roxo datado ~2015; oficina familiar desde 1979; email do dono (mickey@) exposto no site</t>
         </is>
       </c>
-      <c r="K12" s="27" t="inlineStr">
+      <c r="L12" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L12" s="32" t="inlineStr"/>
-      <c r="M12" s="32" t="inlineStr"/>
-      <c r="N12" s="32" t="inlineStr"/>
-      <c r="O12" s="30" t="inlineStr"/>
+      <c r="M12" s="34" t="inlineStr"/>
+      <c r="N12" s="34" t="inlineStr"/>
+      <c r="O12" s="34" t="inlineStr"/>
+      <c r="P12" s="27" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="21" t="n">
@@ -7042,20 +7430,25 @@
       <c r="G13" s="22" t="inlineStr"/>
       <c r="H13" s="24" t="inlineStr"/>
       <c r="I13" s="22" t="inlineStr"/>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="J13" s="31" t="inlineStr">
+        <is>
+          <t>SEM canal direto. Maps. Gancho: visual datado com texto em Arial sobre vídeo; rede local pequena de Phoenix.</t>
+        </is>
+      </c>
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t>Visual datado, video com texto arial; rede local pequena de Phoenix</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr">
+      <c r="L13" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L13" s="31" t="inlineStr"/>
-      <c r="M13" s="31" t="inlineStr"/>
-      <c r="N13" s="31" t="inlineStr"/>
-      <c r="O13" s="25" t="inlineStr"/>
+      <c r="M13" s="32" t="inlineStr"/>
+      <c r="N13" s="32" t="inlineStr"/>
+      <c r="O13" s="32" t="inlineStr"/>
+      <c r="P13" s="22" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="26" t="n">
@@ -7089,20 +7482,25 @@
       <c r="G14" s="27" t="inlineStr"/>
       <c r="H14" s="29" t="inlineStr"/>
       <c r="I14" s="27" t="inlineStr"/>
-      <c r="J14" s="27" t="inlineStr">
+      <c r="J14" s="33" t="inlineStr">
+        <is>
+          <t>SEM canal direto. Maps/Facebook. Gancho: Weebly feito pelo próprio dono, ele já sabe que o site é fraco; prévia com galeria das cercas reais.</t>
+        </is>
+      </c>
+      <c r="K14" s="30" t="inlineStr">
         <is>
           <t>Weebly DIY, tipografia generica, fotos reais; dono fez sozinho</t>
         </is>
       </c>
-      <c r="K14" s="27" t="inlineStr">
+      <c r="L14" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L14" s="32" t="inlineStr"/>
-      <c r="M14" s="32" t="inlineStr"/>
-      <c r="N14" s="32" t="inlineStr"/>
-      <c r="O14" s="30" t="inlineStr"/>
+      <c r="M14" s="34" t="inlineStr"/>
+      <c r="N14" s="34" t="inlineStr"/>
+      <c r="O14" s="34" t="inlineStr"/>
+      <c r="P14" s="27" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="21" t="n">
@@ -7146,20 +7544,25 @@
           <t>csr@westernhvac.com / tom@westernhvac.com / max@westernhvac.com</t>
         </is>
       </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="J15" s="31" t="inlineStr">
+        <is>
+          <t>E-mail tom@ ou max@ (parecem os sócios) ou DM @westernhvac (2.281). Gancho: desde 1967 e Carrier dealer, mas logo 3D dos anos 2000. Empresa grande: espere decisão mais lenta.</t>
+        </is>
+      </c>
+      <c r="K15" s="25" t="inlineStr">
         <is>
           <t>Logo 3D anos 2000, botoes de ticket; desde 1967, Carrier dealer = caixa; decisao pode ser lenta</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="L15" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L15" s="31" t="inlineStr"/>
-      <c r="M15" s="31" t="inlineStr"/>
-      <c r="N15" s="31" t="inlineStr"/>
-      <c r="O15" s="25" t="inlineStr"/>
+      <c r="M15" s="32" t="inlineStr"/>
+      <c r="N15" s="32" t="inlineStr"/>
+      <c r="O15" s="32" t="inlineStr"/>
+      <c r="P15" s="22" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="26" t="n">
@@ -7197,20 +7600,25 @@
           <t>info@sciotolandscaping.com</t>
         </is>
       </c>
-      <c r="J16" s="27" t="inlineStr">
+      <c r="J16" s="33" t="inlineStr">
+        <is>
+          <t>E-mail info@sciotolandscaping.com. Gancho: template de 2012 usando FOTO DE BANCO DE IMAGEM; prévia com os jardins reais que eles fizeram.</t>
+        </is>
+      </c>
+      <c r="K16" s="30" t="inlineStr">
         <is>
           <t>Template 2012 com foto de banco de imagem; info@ visivel no header</t>
         </is>
       </c>
-      <c r="K16" s="27" t="inlineStr">
+      <c r="L16" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L16" s="32" t="inlineStr"/>
-      <c r="M16" s="32" t="inlineStr"/>
-      <c r="N16" s="32" t="inlineStr"/>
-      <c r="O16" s="30" t="inlineStr"/>
+      <c r="M16" s="34" t="inlineStr"/>
+      <c r="N16" s="34" t="inlineStr"/>
+      <c r="O16" s="34" t="inlineStr"/>
+      <c r="P16" s="27" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="21" t="n">
@@ -7248,20 +7656,25 @@
           <t>straightedgepp@gmail.com</t>
         </is>
       </c>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="J17" s="31" t="inlineStr">
+        <is>
+          <t>E-mail straightedgepp@gmail.com (Gmail = negócio pequeno, o dono lê). Gancho: 49 avaliações 4.8 estrelas e o site não mostra isso em lugar nenhum.</t>
+        </is>
+      </c>
+      <c r="K17" s="25" t="inlineStr">
         <is>
           <t>Logo clipart, WP basico; 49 reviews 4.8 = negocio bom com site fraco</t>
         </is>
       </c>
-      <c r="K17" s="22" t="inlineStr">
+      <c r="L17" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L17" s="31" t="inlineStr"/>
-      <c r="M17" s="31" t="inlineStr"/>
-      <c r="N17" s="31" t="inlineStr"/>
-      <c r="O17" s="25" t="inlineStr"/>
+      <c r="M17" s="32" t="inlineStr"/>
+      <c r="N17" s="32" t="inlineStr"/>
+      <c r="O17" s="32" t="inlineStr"/>
+      <c r="P17" s="22" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="26" t="n">
@@ -7305,20 +7718,25 @@
           <t>info@allcreaturespetgrooming.com</t>
         </is>
       </c>
-      <c r="J18" s="27" t="inlineStr">
+      <c r="J18" s="33" t="inlineStr">
+        <is>
+          <t>DM no @allcreaturespetgrooming (3.277) ou e-mail info@. Gancho: Wix com logo duplicado gigante e layout desalinhado; print lado a lado resolve a conversa.</t>
+        </is>
+      </c>
+      <c r="K18" s="30" t="inlineStr">
         <is>
           <t>Wix DIY com logo duplicado gigante e layout desalinhado; tem booking</t>
         </is>
       </c>
-      <c r="K18" s="27" t="inlineStr">
+      <c r="L18" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L18" s="32" t="inlineStr"/>
-      <c r="M18" s="32" t="inlineStr"/>
-      <c r="N18" s="32" t="inlineStr"/>
-      <c r="O18" s="30" t="inlineStr"/>
+      <c r="M18" s="34" t="inlineStr"/>
+      <c r="N18" s="34" t="inlineStr"/>
+      <c r="O18" s="34" t="inlineStr"/>
+      <c r="P18" s="27" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="21" t="n">
@@ -7358,20 +7776,25 @@
         <v>4204</v>
       </c>
       <c r="I19" s="22" t="inlineStr"/>
-      <c r="J19" s="22" t="inlineStr">
+      <c r="J19" s="31" t="inlineStr">
+        <is>
+          <t>DM no @bloombakingco (4.204). SEM e-mail no site. Gancho: padaria artesanal bonita com site sem graça; prévia com as fotos dos produtos que já postam no IG.</t>
+        </is>
+      </c>
+      <c r="K19" s="25" t="inlineStr">
         <is>
           <t>Layout ~2015 (Duda), logo simples; padaria artesanal com IG</t>
         </is>
       </c>
-      <c r="K19" s="22" t="inlineStr">
+      <c r="L19" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L19" s="31" t="inlineStr"/>
-      <c r="M19" s="31" t="inlineStr"/>
-      <c r="N19" s="31" t="inlineStr"/>
-      <c r="O19" s="25" t="inlineStr"/>
+      <c r="M19" s="32" t="inlineStr"/>
+      <c r="N19" s="32" t="inlineStr"/>
+      <c r="O19" s="32" t="inlineStr"/>
+      <c r="P19" s="22" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="26" t="n">
@@ -7409,20 +7832,25 @@
           <t>bluswancarwash@gmail.com</t>
         </is>
       </c>
-      <c r="J20" s="27" t="inlineStr">
+      <c r="J20" s="33" t="inlineStr">
+        <is>
+          <t>E-mail bluswancarwash@gmail.com. Gancho: GoDaddy DIY genérico; prévia com planos e preços claros.</t>
+        </is>
+      </c>
+      <c r="K20" s="30" t="inlineStr">
         <is>
           <t>GoDaddy DIY, 1 unidade; template razoavel mas generico</t>
         </is>
       </c>
-      <c r="K20" s="27" t="inlineStr">
+      <c r="L20" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L20" s="32" t="inlineStr"/>
-      <c r="M20" s="32" t="inlineStr"/>
-      <c r="N20" s="32" t="inlineStr"/>
-      <c r="O20" s="30" t="inlineStr"/>
+      <c r="M20" s="34" t="inlineStr"/>
+      <c r="N20" s="34" t="inlineStr"/>
+      <c r="O20" s="34" t="inlineStr"/>
+      <c r="P20" s="27" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="21" t="n">
@@ -7466,20 +7894,25 @@
           <t>customerservice@alamofencesa.com</t>
         </is>
       </c>
-      <c r="J21" s="22" t="inlineStr">
+      <c r="J21" s="31" t="inlineStr">
+        <is>
+          <t>E-mail customerservice@alamofencesa.com. Gancho: layout centrado antigo. Extra: o IG tem só 88 seguidores, dá pra oferecer site + presença social.</t>
+        </is>
+      </c>
+      <c r="K21" s="25" t="inlineStr">
         <is>
           <t>Layout centrado antigo; customerservice@ exposto; negocio estabelecido</t>
         </is>
       </c>
-      <c r="K21" s="22" t="inlineStr">
+      <c r="L21" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L21" s="31" t="inlineStr"/>
-      <c r="M21" s="31" t="inlineStr"/>
-      <c r="N21" s="31" t="inlineStr"/>
-      <c r="O21" s="25" t="inlineStr"/>
+      <c r="M21" s="32" t="inlineStr"/>
+      <c r="N21" s="32" t="inlineStr"/>
+      <c r="O21" s="32" t="inlineStr"/>
+      <c r="P21" s="22" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="26" t="n">
@@ -7517,20 +7950,25 @@
           <t>service@ims365hvac.com</t>
         </is>
       </c>
-      <c r="J22" s="27" t="inlineStr">
+      <c r="J22" s="33" t="inlineStr">
+        <is>
+          <t>E-mail service@ims365hvac.com. Gancho: 25+ anos de experiência num WordPress genérico com hero cru.</t>
+        </is>
+      </c>
+      <c r="K22" s="30" t="inlineStr">
         <is>
           <t>WP generico, hero cru; empresa 25+ anos</t>
         </is>
       </c>
-      <c r="K22" s="27" t="inlineStr">
+      <c r="L22" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L22" s="32" t="inlineStr"/>
-      <c r="M22" s="32" t="inlineStr"/>
-      <c r="N22" s="32" t="inlineStr"/>
-      <c r="O22" s="30" t="inlineStr"/>
+      <c r="M22" s="34" t="inlineStr"/>
+      <c r="N22" s="34" t="inlineStr"/>
+      <c r="O22" s="34" t="inlineStr"/>
+      <c r="P22" s="27" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="21" t="n">
@@ -7574,20 +8012,25 @@
           <t>orlandoadmin@mawus.com</t>
         </is>
       </c>
-      <c r="J23" s="22" t="inlineStr">
+      <c r="J23" s="31" t="inlineStr">
+        <is>
+          <t>DM no @maworlando (1.049) ou e-mail orlandoadmin@. Gancho: logo dos anos 90; prévia com formulário de aula experimental, que é como academia capta.</t>
+        </is>
+      </c>
+      <c r="K23" s="25" t="inlineStr">
         <is>
           <t>Logo anos 90, layout mediano; academia local com programas</t>
         </is>
       </c>
-      <c r="K23" s="22" t="inlineStr">
+      <c r="L23" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L23" s="31" t="inlineStr"/>
-      <c r="M23" s="31" t="inlineStr"/>
-      <c r="N23" s="31" t="inlineStr"/>
-      <c r="O23" s="25" t="inlineStr"/>
+      <c r="M23" s="32" t="inlineStr"/>
+      <c r="N23" s="32" t="inlineStr"/>
+      <c r="O23" s="32" t="inlineStr"/>
+      <c r="P23" s="22" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="26" t="n">
@@ -7631,20 +8074,25 @@
           <t>powerwashproplus@gmail.com</t>
         </is>
       </c>
-      <c r="J24" s="27" t="inlineStr">
+      <c r="J24" s="33" t="inlineStr">
+        <is>
+          <t>E-mail powerwashproplus@gmail.com. Gancho: Squarespace genérico com logo clipart. O IG tem 7 seguidores: está começando do zero, bom candidato a site + social.</t>
+        </is>
+      </c>
+      <c r="K24" s="30" t="inlineStr">
         <is>
           <t>Squarespace generico, logo clipart, hero fraco; facil mostrar upgrade</t>
         </is>
       </c>
-      <c r="K24" s="27" t="inlineStr">
+      <c r="L24" s="27" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L24" s="32" t="inlineStr"/>
-      <c r="M24" s="32" t="inlineStr"/>
-      <c r="N24" s="32" t="inlineStr"/>
-      <c r="O24" s="30" t="inlineStr"/>
+      <c r="M24" s="34" t="inlineStr"/>
+      <c r="N24" s="34" t="inlineStr"/>
+      <c r="O24" s="34" t="inlineStr"/>
+      <c r="P24" s="27" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="21" t="n">
@@ -7688,23 +8136,28 @@
           <t>tatsbywes97@gmail.com</t>
         </is>
       </c>
-      <c r="J25" s="22" t="inlineStr">
+      <c r="J25" s="31" t="inlineStr">
+        <is>
+          <t>DM no @wes_tattoos_columbus (11K seguidores!). Gancho: artista solo desde 1997, decisão rápida e sem comitê; IG forte mas site simples, prévia com galeria destacada.</t>
+        </is>
+      </c>
+      <c r="K25" s="25" t="inlineStr">
         <is>
           <t>Artista solo desde 1997; site simples escuro; decisao rapida, IG e a vida do tatuador</t>
         </is>
       </c>
-      <c r="K25" s="22" t="inlineStr">
+      <c r="L25" s="22" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="L25" s="31" t="inlineStr"/>
-      <c r="M25" s="31" t="inlineStr"/>
-      <c r="N25" s="31" t="inlineStr"/>
-      <c r="O25" s="25" t="inlineStr"/>
+      <c r="M25" s="32" t="inlineStr"/>
+      <c r="N25" s="32" t="inlineStr"/>
+      <c r="O25" s="32" t="inlineStr"/>
+      <c r="P25" s="22" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O25"/>
+  <autoFilter ref="A4:P25"/>
   <conditionalFormatting sqref="A5:A25">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>8</formula>
@@ -7714,7 +8167,7 @@
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K25">
+  <conditionalFormatting sqref="L5:L25">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="3">
       <formula>"Ganho"</formula>
     </cfRule>
@@ -7726,7 +8179,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="K5:K25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:L25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A fazer,Seguindo,Comentou,DM enviada,Respondeu,Prévia enviada,Negociando,Ganho,Perdido"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9287,24 +9740,24 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>Negócio</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>Site</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>O que verificar</t>
         </is>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Championship Martial Arts</t>
         </is>
@@ -9321,7 +9774,7 @@
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>Kansas City Tree Services</t>
         </is>
@@ -9338,7 +9791,7 @@
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>Purrfect Grooming</t>
         </is>
@@ -9355,7 +9808,7 @@
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Redes grandes (nota 1-3)</t>
         </is>
@@ -9372,7 +9825,7 @@
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>E-mails genéricos</t>
         </is>
